--- a/research/traditional_assets/database/data/argentina/argentina_building_materials.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_building_materials.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2331693381898678</v>
+        <v>0.2323824955062033</v>
       </c>
       <c r="C2">
-        <v>203.9469125485928</v>
+        <v>202.7071479998856</v>
       </c>
       <c r="D2">
-        <v>189.0469125485928</v>
+        <v>189.8441479998856</v>
       </c>
       <c r="E2">
-        <v>-14.5</v>
+        <v>-12.463</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.037</v>
       </c>
       <c r="G2">
         <v>14.9</v>
@@ -1451,28 +1451,28 @@
         <v>32.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1024611</v>
       </c>
       <c r="N2">
-        <v>32.9</v>
+        <v>32.7975389</v>
       </c>
       <c r="O2">
-        <v>11.515</v>
+        <v>11.479138615</v>
       </c>
       <c r="P2">
-        <v>21.385</v>
+        <v>21.318400285</v>
       </c>
       <c r="Q2">
-        <v>26.285</v>
+        <v>26.218400285</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2331693381898678</v>
+        <v>0.2343995409153569</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9266597384696744</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>321.0974701618468</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2323824955062033</v>
+        <v>0.2315956528225387</v>
       </c>
       <c r="C3">
-        <v>202.7071479998856</v>
+        <v>201.4741360190935</v>
       </c>
       <c r="D3">
-        <v>189.8441479998856</v>
+        <v>190.6481360190936</v>
       </c>
       <c r="E3">
-        <v>-12.463</v>
+        <v>-10.426</v>
       </c>
       <c r="F3">
-        <v>2.037</v>
+        <v>4.074</v>
       </c>
       <c r="G3">
         <v>14.9</v>
@@ -1533,28 +1533,28 @@
         <v>32.9</v>
       </c>
       <c r="M3">
-        <v>0.1024611</v>
+        <v>0.2049222</v>
       </c>
       <c r="N3">
-        <v>32.7975389</v>
+        <v>32.6950778</v>
       </c>
       <c r="O3">
-        <v>11.479138615</v>
+        <v>11.44327723</v>
       </c>
       <c r="P3">
-        <v>21.318400285</v>
+        <v>21.25180057</v>
       </c>
       <c r="Q3">
-        <v>26.218400285</v>
+        <v>26.15180057</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2343995409153569</v>
+        <v>0.2356548498189171</v>
       </c>
       <c r="T3">
-        <v>0.9266597384696744</v>
+        <v>0.9328275383202256</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>321.0974701618468</v>
+        <v>160.5487350809234</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2315956528225387</v>
+        <v>0.2308088101388742</v>
       </c>
       <c r="C4">
-        <v>201.4741360190935</v>
+        <v>200.2479627622541</v>
       </c>
       <c r="D4">
-        <v>190.6481360190936</v>
+        <v>191.4589627622541</v>
       </c>
       <c r="E4">
-        <v>-10.426</v>
+        <v>-8.389000000000003</v>
       </c>
       <c r="F4">
-        <v>4.074</v>
+        <v>6.111</v>
       </c>
       <c r="G4">
         <v>14.9</v>
@@ -1615,28 +1615,28 @@
         <v>32.9</v>
       </c>
       <c r="M4">
-        <v>0.2049222</v>
+        <v>0.3073833</v>
       </c>
       <c r="N4">
-        <v>32.6950778</v>
+        <v>32.5926167</v>
       </c>
       <c r="O4">
-        <v>11.44327723</v>
+        <v>11.407415845</v>
       </c>
       <c r="P4">
-        <v>21.25180057</v>
+        <v>21.185200855</v>
       </c>
       <c r="Q4">
-        <v>26.15180057</v>
+        <v>26.085200855</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2356548498189171</v>
+        <v>0.2369360413802827</v>
       </c>
       <c r="T4">
-        <v>0.9328275383202256</v>
+        <v>0.939122509301716</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>160.5487350809234</v>
+        <v>107.0324900539489</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2308088101388742</v>
+        <v>0.2300219674552096</v>
       </c>
       <c r="C5">
-        <v>200.2479627622541</v>
+        <v>199.0287158573518</v>
       </c>
       <c r="D5">
-        <v>191.4589627622541</v>
+        <v>192.2767158573518</v>
       </c>
       <c r="E5">
-        <v>-8.389000000000003</v>
+        <v>-6.352000000000002</v>
       </c>
       <c r="F5">
-        <v>6.111</v>
+        <v>8.148</v>
       </c>
       <c r="G5">
         <v>14.9</v>
@@ -1697,28 +1697,28 @@
         <v>32.9</v>
       </c>
       <c r="M5">
-        <v>0.3073833</v>
+        <v>0.4098443999999999</v>
       </c>
       <c r="N5">
-        <v>32.5926167</v>
+        <v>32.4901556</v>
       </c>
       <c r="O5">
-        <v>11.407415845</v>
+        <v>11.37155446</v>
       </c>
       <c r="P5">
-        <v>21.185200855</v>
+        <v>21.11860114</v>
       </c>
       <c r="Q5">
-        <v>26.085200855</v>
+        <v>26.01860114</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2369360413802827</v>
+        <v>0.23824392443251</v>
       </c>
       <c r="T5">
-        <v>0.939122509301716</v>
+        <v>0.9455486255119876</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>107.0324900539489</v>
+        <v>80.27436754046171</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2300219674552096</v>
+        <v>0.2292351247715451</v>
       </c>
       <c r="C6">
-        <v>199.0287158573518</v>
+        <v>197.8164844358878</v>
       </c>
       <c r="D6">
-        <v>192.2767158573518</v>
+        <v>193.1014844358878</v>
       </c>
       <c r="E6">
-        <v>-6.352000000000002</v>
+        <v>-4.315000000000001</v>
       </c>
       <c r="F6">
-        <v>8.148</v>
+        <v>10.185</v>
       </c>
       <c r="G6">
         <v>14.9</v>
@@ -1779,28 +1779,28 @@
         <v>32.9</v>
       </c>
       <c r="M6">
-        <v>0.4098443999999999</v>
+        <v>0.5123055</v>
       </c>
       <c r="N6">
-        <v>32.4901556</v>
+        <v>32.3876945</v>
       </c>
       <c r="O6">
-        <v>11.37155446</v>
+        <v>11.335693075</v>
       </c>
       <c r="P6">
-        <v>21.11860114</v>
+        <v>21.052001425</v>
       </c>
       <c r="Q6">
-        <v>26.01860114</v>
+        <v>25.952001425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.23824392443251</v>
+        <v>0.2395793418647843</v>
       </c>
       <c r="T6">
-        <v>0.9455486255119876</v>
+        <v>0.9521100283793176</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>80.27436754046171</v>
+        <v>64.21949403236937</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2292351247715451</v>
+        <v>0.2284482820878806</v>
       </c>
       <c r="C7">
-        <v>197.8164844358878</v>
+        <v>196.6113591652654</v>
       </c>
       <c r="D7">
-        <v>193.1014844358878</v>
+        <v>193.9333591652654</v>
       </c>
       <c r="E7">
-        <v>-4.315000000000001</v>
+        <v>-2.278000000000002</v>
       </c>
       <c r="F7">
-        <v>10.185</v>
+        <v>12.222</v>
       </c>
       <c r="G7">
         <v>14.9</v>
@@ -1861,28 +1861,28 @@
         <v>32.9</v>
       </c>
       <c r="M7">
-        <v>0.5123055</v>
+        <v>0.6147665999999999</v>
       </c>
       <c r="N7">
-        <v>32.3876945</v>
+        <v>32.2852334</v>
       </c>
       <c r="O7">
-        <v>11.335693075</v>
+        <v>11.29983169</v>
       </c>
       <c r="P7">
-        <v>21.052001425</v>
+        <v>20.98540171</v>
       </c>
       <c r="Q7">
-        <v>25.952001425</v>
+        <v>25.88540171</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2395793418647843</v>
+        <v>0.2409431724339155</v>
       </c>
       <c r="T7">
-        <v>0.9521100283793176</v>
+        <v>0.9588110355629736</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>64.21949403236937</v>
+        <v>53.51624502697446</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2284482820878806</v>
+        <v>0.227661439404216</v>
       </c>
       <c r="C8">
-        <v>196.6113591652654</v>
+        <v>195.4134322820161</v>
       </c>
       <c r="D8">
-        <v>193.9333591652654</v>
+        <v>194.7724322820161</v>
       </c>
       <c r="E8">
-        <v>-2.278000000000002</v>
+        <v>-0.2410000000000032</v>
       </c>
       <c r="F8">
-        <v>12.222</v>
+        <v>14.259</v>
       </c>
       <c r="G8">
         <v>14.9</v>
@@ -1943,28 +1943,28 @@
         <v>32.9</v>
       </c>
       <c r="M8">
-        <v>0.6147665999999999</v>
+        <v>0.7172276999999999</v>
       </c>
       <c r="N8">
-        <v>32.2852334</v>
+        <v>32.1827723</v>
       </c>
       <c r="O8">
-        <v>11.29983169</v>
+        <v>11.263970305</v>
       </c>
       <c r="P8">
-        <v>20.98540171</v>
+        <v>20.918801995</v>
       </c>
       <c r="Q8">
-        <v>25.88540171</v>
+        <v>25.818801995</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2409431724339155</v>
+        <v>0.2423363326927054</v>
       </c>
       <c r="T8">
-        <v>0.9588110355629736</v>
+        <v>0.9656561504279986</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>53.51624502697446</v>
+        <v>45.87106716597811</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.227661439404216</v>
+        <v>0.2268745967205515</v>
       </c>
       <c r="C9">
-        <v>195.4134322820162</v>
+        <v>194.2227976258924</v>
       </c>
       <c r="D9">
-        <v>194.7724322820162</v>
+        <v>195.6187976258924</v>
       </c>
       <c r="E9">
-        <v>-0.2410000000000014</v>
+        <v>1.795999999999998</v>
       </c>
       <c r="F9">
-        <v>14.259</v>
+        <v>16.296</v>
       </c>
       <c r="G9">
         <v>14.9</v>
@@ -2025,28 +2025,28 @@
         <v>32.9</v>
       </c>
       <c r="M9">
-        <v>0.7172277</v>
+        <v>0.8196887999999999</v>
       </c>
       <c r="N9">
-        <v>32.1827723</v>
+        <v>32.0803112</v>
       </c>
       <c r="O9">
-        <v>11.263970305</v>
+        <v>11.22810892</v>
       </c>
       <c r="P9">
-        <v>20.918801995</v>
+        <v>20.85220228</v>
       </c>
       <c r="Q9">
-        <v>25.818801995</v>
+        <v>25.75220228</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2423363326927054</v>
+        <v>0.2437597790440777</v>
       </c>
       <c r="T9">
-        <v>0.9656561504279986</v>
+        <v>0.9726500721379154</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.8710671659781</v>
+        <v>40.13718377023085</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2268745967205515</v>
+        <v>0.2260877540368869</v>
       </c>
       <c r="C10">
-        <v>194.2227976258924</v>
+        <v>193.0395506748527</v>
       </c>
       <c r="D10">
-        <v>195.6187976258924</v>
+        <v>196.4725506748527</v>
       </c>
       <c r="E10">
-        <v>1.795999999999998</v>
+        <v>3.832999999999997</v>
       </c>
       <c r="F10">
-        <v>16.296</v>
+        <v>18.333</v>
       </c>
       <c r="G10">
         <v>14.9</v>
@@ -2107,28 +2107,28 @@
         <v>32.9</v>
       </c>
       <c r="M10">
-        <v>0.8196887999999999</v>
+        <v>0.9221498999999999</v>
       </c>
       <c r="N10">
-        <v>32.0803112</v>
+        <v>31.9778501</v>
       </c>
       <c r="O10">
-        <v>11.22810892</v>
+        <v>11.192247535</v>
       </c>
       <c r="P10">
-        <v>20.85220228</v>
+        <v>20.785602565</v>
       </c>
       <c r="Q10">
-        <v>25.75220228</v>
+        <v>25.685602565</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2437597790440777</v>
+        <v>0.245214509930645</v>
       </c>
       <c r="T10">
-        <v>0.9726500721379154</v>
+        <v>0.9797977064128854</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.13718377023085</v>
+        <v>35.67749668464965</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2260877540368869</v>
+        <v>0.2253009113532224</v>
       </c>
       <c r="C11">
-        <v>193.0395506748527</v>
+        <v>191.8637885809667</v>
       </c>
       <c r="D11">
-        <v>196.4725506748527</v>
+        <v>197.3337885809667</v>
       </c>
       <c r="E11">
-        <v>3.832999999999997</v>
+        <v>5.869999999999996</v>
       </c>
       <c r="F11">
-        <v>18.333</v>
+        <v>20.37</v>
       </c>
       <c r="G11">
         <v>14.9</v>
@@ -2189,28 +2189,28 @@
         <v>32.9</v>
       </c>
       <c r="M11">
-        <v>0.9221498999999999</v>
+        <v>1.024611</v>
       </c>
       <c r="N11">
-        <v>31.9778501</v>
+        <v>31.875389</v>
       </c>
       <c r="O11">
-        <v>11.192247535</v>
+        <v>11.15638615</v>
       </c>
       <c r="P11">
-        <v>20.785602565</v>
+        <v>20.71900285</v>
       </c>
       <c r="Q11">
-        <v>25.685602565</v>
+        <v>25.61900285</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.245214509930645</v>
+        <v>0.2467015681702471</v>
       </c>
       <c r="T11">
-        <v>0.9797977064128854</v>
+        <v>0.987104177005077</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.67749668464965</v>
+        <v>32.10974701618468</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2253009113532224</v>
+        <v>0.2245140686695579</v>
       </c>
       <c r="C12">
-        <v>191.8637885809667</v>
+        <v>190.6956102072699</v>
       </c>
       <c r="D12">
-        <v>197.3337885809667</v>
+        <v>198.2026102072699</v>
       </c>
       <c r="E12">
-        <v>5.869999999999999</v>
+        <v>7.906999999999998</v>
       </c>
       <c r="F12">
-        <v>20.37</v>
+        <v>22.407</v>
       </c>
       <c r="G12">
         <v>14.9</v>
@@ -2271,28 +2271,28 @@
         <v>32.9</v>
       </c>
       <c r="M12">
-        <v>1.024611</v>
+        <v>1.1270721</v>
       </c>
       <c r="N12">
-        <v>31.875389</v>
+        <v>31.7729279</v>
       </c>
       <c r="O12">
-        <v>11.15638615</v>
+        <v>11.120524765</v>
       </c>
       <c r="P12">
-        <v>20.71900285</v>
+        <v>20.652403135</v>
       </c>
       <c r="Q12">
-        <v>25.61900285</v>
+        <v>25.552403135</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2467015681702471</v>
+        <v>0.2482220434489415</v>
       </c>
       <c r="T12">
-        <v>0.987104177005077</v>
+        <v>0.994574837947655</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.10974701618468</v>
+        <v>29.19067910562244</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2245140686695579</v>
+        <v>0.2237272259858933</v>
       </c>
       <c r="C13">
-        <v>190.6956102072699</v>
+        <v>189.5351161655945</v>
       </c>
       <c r="D13">
-        <v>198.2026102072699</v>
+        <v>199.0791161655945</v>
       </c>
       <c r="E13">
-        <v>7.906999999999998</v>
+        <v>9.943999999999997</v>
       </c>
       <c r="F13">
-        <v>22.407</v>
+        <v>24.444</v>
       </c>
       <c r="G13">
         <v>14.9</v>
@@ -2353,28 +2353,28 @@
         <v>32.9</v>
       </c>
       <c r="M13">
-        <v>1.1270721</v>
+        <v>1.2295332</v>
       </c>
       <c r="N13">
-        <v>31.7729279</v>
+        <v>31.6704668</v>
       </c>
       <c r="O13">
-        <v>11.120524765</v>
+        <v>11.08466338</v>
       </c>
       <c r="P13">
-        <v>20.652403135</v>
+        <v>20.58580342</v>
       </c>
       <c r="Q13">
-        <v>25.552403135</v>
+        <v>25.48580342</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2482220434489415</v>
+        <v>0.2497770749839697</v>
       </c>
       <c r="T13">
-        <v>0.994574837947655</v>
+        <v>1.002215286638928</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.19067910562244</v>
+        <v>26.75812251348723</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2237272259858933</v>
+        <v>0.2229403833022288</v>
       </c>
       <c r="C14">
-        <v>189.5351161655945</v>
+        <v>188.3824088554102</v>
       </c>
       <c r="D14">
-        <v>199.0791161655945</v>
+        <v>199.9634088554102</v>
       </c>
       <c r="E14">
-        <v>9.943999999999997</v>
+        <v>11.981</v>
       </c>
       <c r="F14">
-        <v>24.444</v>
+        <v>26.481</v>
       </c>
       <c r="G14">
         <v>14.9</v>
@@ -2435,28 +2435,28 @@
         <v>32.9</v>
       </c>
       <c r="M14">
-        <v>1.2295332</v>
+        <v>1.3319943</v>
       </c>
       <c r="N14">
-        <v>31.6704668</v>
+        <v>31.5680057</v>
       </c>
       <c r="O14">
-        <v>11.08466338</v>
+        <v>11.048801995</v>
       </c>
       <c r="P14">
-        <v>20.58580342</v>
+        <v>20.519203705</v>
       </c>
       <c r="Q14">
-        <v>25.48580342</v>
+        <v>25.419203705</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2497770749839697</v>
+        <v>0.2513678543703779</v>
       </c>
       <c r="T14">
-        <v>1.002215286638928</v>
+        <v>1.01003137782885</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.75812251348723</v>
+        <v>24.69980539706514</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2229403833022288</v>
+        <v>0.2221535406185643</v>
       </c>
       <c r="C15">
-        <v>188.3824088554102</v>
+        <v>187.2375925037034</v>
       </c>
       <c r="D15">
-        <v>199.9634088554102</v>
+        <v>200.8555925037034</v>
       </c>
       <c r="E15">
-        <v>11.981</v>
+        <v>14.018</v>
       </c>
       <c r="F15">
-        <v>26.481</v>
+        <v>28.518</v>
       </c>
       <c r="G15">
         <v>14.9</v>
@@ -2517,28 +2517,28 @@
         <v>32.9</v>
       </c>
       <c r="M15">
-        <v>1.3319943</v>
+        <v>1.4344554</v>
       </c>
       <c r="N15">
-        <v>31.5680057</v>
+        <v>31.4655446</v>
       </c>
       <c r="O15">
-        <v>11.048801995</v>
+        <v>11.01294061</v>
       </c>
       <c r="P15">
-        <v>20.519203705</v>
+        <v>20.45260399</v>
       </c>
       <c r="Q15">
-        <v>25.419203705</v>
+        <v>25.35260399</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2513678543703779</v>
+        <v>0.2529956286262375</v>
       </c>
       <c r="T15">
-        <v>1.01003137782885</v>
+        <v>1.01802923858133</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.69980539706514</v>
+        <v>22.93553358298906</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2221535406185643</v>
+        <v>0.2213666979348997</v>
       </c>
       <c r="C16">
-        <v>187.2375925037034</v>
+        <v>186.10077320593</v>
       </c>
       <c r="D16">
-        <v>200.8555925037034</v>
+        <v>201.75577320593</v>
       </c>
       <c r="E16">
-        <v>14.018</v>
+        <v>16.055</v>
       </c>
       <c r="F16">
-        <v>28.518</v>
+        <v>30.555</v>
       </c>
       <c r="G16">
         <v>14.9</v>
@@ -2599,28 +2599,28 @@
         <v>32.9</v>
       </c>
       <c r="M16">
-        <v>1.4344554</v>
+        <v>1.5369165</v>
       </c>
       <c r="N16">
-        <v>31.4655446</v>
+        <v>31.3630835</v>
       </c>
       <c r="O16">
-        <v>11.01294061</v>
+        <v>10.977079225</v>
       </c>
       <c r="P16">
-        <v>20.45260399</v>
+        <v>20.386004275</v>
       </c>
       <c r="Q16">
-        <v>25.35260399</v>
+        <v>25.286004275</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2529956286262375</v>
+        <v>0.2546617034528232</v>
       </c>
       <c r="T16">
-        <v>1.01802923858133</v>
+        <v>1.026215284292691</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.93553358298906</v>
+        <v>21.40649801078979</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2213666979348997</v>
+        <v>0.2205798552512352</v>
       </c>
       <c r="C17">
-        <v>186.10077320593</v>
+        <v>184.9720589680734</v>
       </c>
       <c r="D17">
-        <v>201.75577320593</v>
+        <v>202.6640589680734</v>
       </c>
       <c r="E17">
-        <v>16.05499999999999</v>
+        <v>18.092</v>
       </c>
       <c r="F17">
-        <v>30.555</v>
+        <v>32.592</v>
       </c>
       <c r="G17">
         <v>14.9</v>
@@ -2681,28 +2681,28 @@
         <v>32.9</v>
       </c>
       <c r="M17">
-        <v>1.5369165</v>
+        <v>1.6393776</v>
       </c>
       <c r="N17">
-        <v>31.3630835</v>
+        <v>31.2606224</v>
       </c>
       <c r="O17">
-        <v>10.977079225</v>
+        <v>10.94121784</v>
       </c>
       <c r="P17">
-        <v>20.386004275</v>
+        <v>20.31940456</v>
       </c>
       <c r="Q17">
-        <v>25.286004275</v>
+        <v>25.21940456</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2546617034528232</v>
+        <v>0.2563674467276609</v>
       </c>
       <c r="T17">
-        <v>1.026215284292691</v>
+        <v>1.034596235854322</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.40649801078979</v>
+        <v>20.06859188511543</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2205798552512352</v>
+        <v>0.2197930125675707</v>
       </c>
       <c r="C18">
-        <v>184.9720589680734</v>
+        <v>183.8515597498439</v>
       </c>
       <c r="D18">
-        <v>202.6640589680734</v>
+        <v>203.5805597498438</v>
       </c>
       <c r="E18">
-        <v>18.092</v>
+        <v>20.129</v>
       </c>
       <c r="F18">
-        <v>32.592</v>
+        <v>34.629</v>
       </c>
       <c r="G18">
         <v>14.9</v>
@@ -2763,28 +2763,28 @@
         <v>32.9</v>
       </c>
       <c r="M18">
-        <v>1.6393776</v>
+        <v>1.7418387</v>
       </c>
       <c r="N18">
-        <v>31.2606224</v>
+        <v>31.1581613</v>
       </c>
       <c r="O18">
-        <v>10.94121784</v>
+        <v>10.905356455</v>
       </c>
       <c r="P18">
-        <v>20.31940456</v>
+        <v>20.252804845</v>
       </c>
       <c r="Q18">
-        <v>25.21940456</v>
+        <v>25.152804845</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2563674467276609</v>
+        <v>0.2581142922500851</v>
       </c>
       <c r="T18">
-        <v>1.034596235854322</v>
+        <v>1.043179138055993</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.06859188511543</v>
+        <v>18.88808648010864</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2197930125675707</v>
+        <v>0.2190061698839061</v>
       </c>
       <c r="C19">
-        <v>183.8515597498439</v>
+        <v>182.7393875090563</v>
       </c>
       <c r="D19">
-        <v>203.5805597498438</v>
+        <v>204.5053875090563</v>
       </c>
       <c r="E19">
-        <v>20.129</v>
+        <v>22.166</v>
       </c>
       <c r="F19">
-        <v>34.629</v>
+        <v>36.666</v>
       </c>
       <c r="G19">
         <v>14.9</v>
@@ -2845,28 +2845,28 @@
         <v>32.9</v>
       </c>
       <c r="M19">
-        <v>1.7418387</v>
+        <v>1.8442998</v>
       </c>
       <c r="N19">
-        <v>31.1581613</v>
+        <v>31.0557002</v>
       </c>
       <c r="O19">
-        <v>10.905356455</v>
+        <v>10.86949507</v>
       </c>
       <c r="P19">
-        <v>20.252804845</v>
+        <v>20.18620513</v>
       </c>
       <c r="Q19">
-        <v>25.152804845</v>
+        <v>25.08620513</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2581142922500851</v>
+        <v>0.2599037437608611</v>
       </c>
       <c r="T19">
-        <v>1.043179138055993</v>
+        <v>1.051971379335753</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.88808648010864</v>
+        <v>17.83874834232482</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2190061698839061</v>
+        <v>0.2182193272002416</v>
       </c>
       <c r="C20">
-        <v>182.7393875090563</v>
+        <v>181.6356562472216</v>
       </c>
       <c r="D20">
-        <v>204.5053875090563</v>
+        <v>205.4386562472216</v>
       </c>
       <c r="E20">
-        <v>22.166</v>
+        <v>24.203</v>
       </c>
       <c r="F20">
-        <v>36.666</v>
+        <v>38.703</v>
       </c>
       <c r="G20">
         <v>14.9</v>
@@ -2927,28 +2927,28 @@
         <v>32.9</v>
       </c>
       <c r="M20">
-        <v>1.8442998</v>
+        <v>1.9467609</v>
       </c>
       <c r="N20">
-        <v>31.0557002</v>
+        <v>30.9532391</v>
       </c>
       <c r="O20">
-        <v>10.86949507</v>
+        <v>10.833633685</v>
       </c>
       <c r="P20">
-        <v>20.18620513</v>
+        <v>20.119605415</v>
       </c>
       <c r="Q20">
-        <v>25.08620513</v>
+        <v>25.019605415</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2599037437608611</v>
+        <v>0.2617373792595575</v>
       </c>
       <c r="T20">
-        <v>1.051971379335753</v>
+        <v>1.060980712992792</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.83874834232482</v>
+        <v>16.89986685062352</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2182193272002416</v>
+        <v>0.217432484516577</v>
       </c>
       <c r="C21">
-        <v>181.6356562472216</v>
+        <v>180.5404820563934</v>
       </c>
       <c r="D21">
-        <v>205.4386562472216</v>
+        <v>206.3804820563934</v>
       </c>
       <c r="E21">
-        <v>24.203</v>
+        <v>26.24</v>
       </c>
       <c r="F21">
-        <v>38.703</v>
+        <v>40.74</v>
       </c>
       <c r="G21">
         <v>14.9</v>
@@ -3009,28 +3009,28 @@
         <v>32.9</v>
       </c>
       <c r="M21">
-        <v>1.9467609</v>
+        <v>2.049222</v>
       </c>
       <c r="N21">
-        <v>30.9532391</v>
+        <v>30.850778</v>
       </c>
       <c r="O21">
-        <v>10.833633685</v>
+        <v>10.7977723</v>
       </c>
       <c r="P21">
-        <v>20.119605415</v>
+        <v>20.0530057</v>
       </c>
       <c r="Q21">
-        <v>25.019605415</v>
+        <v>24.9530057</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2617373792595575</v>
+        <v>0.2636168556457213</v>
       </c>
       <c r="T21">
-        <v>1.060980712992792</v>
+        <v>1.070215279991256</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.89986685062352</v>
+        <v>16.05487350809234</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.217432484516577</v>
+        <v>0.2166456418329125</v>
       </c>
       <c r="C22">
-        <v>180.5404820563934</v>
+        <v>179.4539831673088</v>
       </c>
       <c r="D22">
-        <v>206.3804820563934</v>
+        <v>207.3309831673088</v>
       </c>
       <c r="E22">
-        <v>26.24</v>
+        <v>28.277</v>
       </c>
       <c r="F22">
-        <v>40.74</v>
+        <v>42.777</v>
       </c>
       <c r="G22">
         <v>14.9</v>
@@ -3091,28 +3091,28 @@
         <v>32.9</v>
       </c>
       <c r="M22">
-        <v>2.049222</v>
+        <v>2.1516831</v>
       </c>
       <c r="N22">
-        <v>30.850778</v>
+        <v>30.7483169</v>
       </c>
       <c r="O22">
-        <v>10.7977723</v>
+        <v>10.761910915</v>
       </c>
       <c r="P22">
-        <v>20.0530057</v>
+        <v>19.986405985</v>
       </c>
       <c r="Q22">
-        <v>24.9530057</v>
+        <v>24.886405985</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2636168556457213</v>
+        <v>0.2655439137125474</v>
       </c>
       <c r="T22">
-        <v>1.070215279991256</v>
+        <v>1.07968363349601</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.05487350809234</v>
+        <v>15.2903557219927</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2166456418329125</v>
+        <v>0.215858799149248</v>
       </c>
       <c r="C23">
-        <v>179.4539831673088</v>
+        <v>178.3762799988652</v>
       </c>
       <c r="D23">
-        <v>207.3309831673088</v>
+        <v>208.2902799988652</v>
       </c>
       <c r="E23">
-        <v>28.27699999999999</v>
+        <v>30.314</v>
       </c>
       <c r="F23">
-        <v>42.77699999999999</v>
+        <v>44.814</v>
       </c>
       <c r="G23">
         <v>14.9</v>
@@ -3173,28 +3173,28 @@
         <v>32.9</v>
       </c>
       <c r="M23">
-        <v>2.1516831</v>
+        <v>2.2541442</v>
       </c>
       <c r="N23">
-        <v>30.7483169</v>
+        <v>30.6458558</v>
       </c>
       <c r="O23">
-        <v>10.761910915</v>
+        <v>10.72604953</v>
       </c>
       <c r="P23">
-        <v>19.986405985</v>
+        <v>19.91980627</v>
       </c>
       <c r="Q23">
-        <v>24.886405985</v>
+        <v>24.81980627</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2655439137125474</v>
+        <v>0.2675203835246769</v>
       </c>
       <c r="T23">
-        <v>1.07968363349601</v>
+        <v>1.089394765295759</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.29035572199271</v>
+        <v>14.59533955281122</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.215858799149248</v>
+        <v>0.2150719564655834</v>
       </c>
       <c r="C24">
-        <v>178.3762799988652</v>
+        <v>177.3074952089782</v>
       </c>
       <c r="D24">
-        <v>208.2902799988652</v>
+        <v>209.2584952089782</v>
       </c>
       <c r="E24">
-        <v>30.314</v>
+        <v>32.351</v>
       </c>
       <c r="F24">
-        <v>44.814</v>
+        <v>46.851</v>
       </c>
       <c r="G24">
         <v>14.9</v>
@@ -3255,28 +3255,28 @@
         <v>32.9</v>
       </c>
       <c r="M24">
-        <v>2.2541442</v>
+        <v>2.3566053</v>
       </c>
       <c r="N24">
-        <v>30.6458558</v>
+        <v>30.5433947</v>
       </c>
       <c r="O24">
-        <v>10.72604953</v>
+        <v>10.690188145</v>
       </c>
       <c r="P24">
-        <v>19.91980627</v>
+        <v>19.853206555</v>
       </c>
       <c r="Q24">
-        <v>24.81980627</v>
+        <v>24.753206555</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2675203835246769</v>
+        <v>0.2695481902150434</v>
       </c>
       <c r="T24">
-        <v>1.089394765295759</v>
+        <v>1.099358134285111</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.59533955281122</v>
+        <v>13.96075957225421</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2150719564655834</v>
+        <v>0.2142851137819189</v>
       </c>
       <c r="C25">
-        <v>177.3074952089782</v>
+        <v>176.2477537468627</v>
       </c>
       <c r="D25">
-        <v>209.2584952089782</v>
+        <v>210.2357537468627</v>
       </c>
       <c r="E25">
-        <v>32.351</v>
+        <v>34.388</v>
       </c>
       <c r="F25">
-        <v>46.851</v>
+        <v>48.888</v>
       </c>
       <c r="G25">
         <v>14.9</v>
@@ -3337,28 +3337,28 @@
         <v>32.9</v>
       </c>
       <c r="M25">
-        <v>2.3566053</v>
+        <v>2.4590664</v>
       </c>
       <c r="N25">
-        <v>30.5433947</v>
+        <v>30.4409336</v>
       </c>
       <c r="O25">
-        <v>10.690188145</v>
+        <v>10.65432676</v>
       </c>
       <c r="P25">
-        <v>19.853206555</v>
+        <v>19.78660684</v>
       </c>
       <c r="Q25">
-        <v>24.753206555</v>
+        <v>24.68660684</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2695481902150434</v>
+        <v>0.271629360239367</v>
       </c>
       <c r="T25">
-        <v>1.099358134285111</v>
+        <v>1.109583697195235</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.96075957225421</v>
+        <v>13.37906125674362</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2142851137819189</v>
+        <v>0.2137420210982544</v>
       </c>
       <c r="C26">
-        <v>176.2477537468627</v>
+        <v>174.8906163503848</v>
       </c>
       <c r="D26">
-        <v>210.2357537468627</v>
+        <v>210.9156163503848</v>
       </c>
       <c r="E26">
-        <v>34.388</v>
+        <v>36.425</v>
       </c>
       <c r="F26">
-        <v>48.888</v>
+        <v>50.925</v>
       </c>
       <c r="G26">
         <v>14.9</v>
@@ -3419,45 +3419,45 @@
         <v>32.9</v>
       </c>
       <c r="M26">
-        <v>2.4590664</v>
+        <v>2.637915</v>
       </c>
       <c r="N26">
-        <v>30.4409336</v>
+        <v>30.262085</v>
       </c>
       <c r="O26">
-        <v>10.65432676</v>
+        <v>10.59172975</v>
       </c>
       <c r="P26">
-        <v>19.78660684</v>
+        <v>19.67035525</v>
       </c>
       <c r="Q26">
-        <v>24.68660684</v>
+        <v>24.57035525</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.271629360239367</v>
+        <v>0.2737660281310058</v>
       </c>
       <c r="T26">
-        <v>1.109583697195235</v>
+        <v>1.120081941782963</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.37906125674362</v>
+        <v>12.47197123485783</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2137420210982544</v>
+        <v>0.2129649284145898</v>
       </c>
       <c r="C27">
-        <v>174.8906163503848</v>
+        <v>173.8340910461894</v>
       </c>
       <c r="D27">
-        <v>210.9156163503848</v>
+        <v>211.8960910461894</v>
       </c>
       <c r="E27">
-        <v>36.425</v>
+        <v>38.462</v>
       </c>
       <c r="F27">
-        <v>50.925</v>
+        <v>52.962</v>
       </c>
       <c r="G27">
         <v>14.9</v>
@@ -3501,28 +3501,28 @@
         <v>32.9</v>
       </c>
       <c r="M27">
-        <v>2.637915</v>
+        <v>2.7434316</v>
       </c>
       <c r="N27">
-        <v>30.262085</v>
+        <v>30.1565684</v>
       </c>
       <c r="O27">
-        <v>10.59172975</v>
+        <v>10.55479894</v>
       </c>
       <c r="P27">
-        <v>19.67035525</v>
+        <v>19.60176946</v>
       </c>
       <c r="Q27">
-        <v>24.57035525</v>
+        <v>24.50176946</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2737660281310058</v>
+        <v>0.2759604438034997</v>
       </c>
       <c r="T27">
-        <v>1.120081941782963</v>
+        <v>1.1308639227109</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.47197123485783</v>
+        <v>11.99228003351715</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2129649284145898</v>
+        <v>0.2121878357309253</v>
       </c>
       <c r="C28">
-        <v>173.8340910461894</v>
+        <v>172.7867241003472</v>
       </c>
       <c r="D28">
-        <v>211.8960910461894</v>
+        <v>212.8857241003472</v>
       </c>
       <c r="E28">
-        <v>38.462</v>
+        <v>40.499</v>
       </c>
       <c r="F28">
-        <v>52.962</v>
+        <v>54.999</v>
       </c>
       <c r="G28">
         <v>14.9</v>
@@ -3583,28 +3583,28 @@
         <v>32.9</v>
       </c>
       <c r="M28">
-        <v>2.7434316</v>
+        <v>2.8489482</v>
       </c>
       <c r="N28">
-        <v>30.1565684</v>
+        <v>30.0510518</v>
       </c>
       <c r="O28">
-        <v>10.55479894</v>
+        <v>10.51786813</v>
       </c>
       <c r="P28">
-        <v>19.60176946</v>
+        <v>19.53318367</v>
       </c>
       <c r="Q28">
-        <v>24.50176946</v>
+        <v>24.43318367</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2759604438034997</v>
+        <v>0.2782149804533223</v>
       </c>
       <c r="T28">
-        <v>1.1308639227109</v>
+        <v>1.141941300376588</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.99228003351715</v>
+        <v>11.54812151375725</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2121878357309253</v>
+        <v>0.2114107430472607</v>
       </c>
       <c r="C29">
-        <v>172.7867241003472</v>
+        <v>171.7486444337207</v>
       </c>
       <c r="D29">
-        <v>212.8857241003472</v>
+        <v>213.8846444337207</v>
       </c>
       <c r="E29">
-        <v>40.499</v>
+        <v>42.536</v>
       </c>
       <c r="F29">
-        <v>54.999</v>
+        <v>57.036</v>
       </c>
       <c r="G29">
         <v>14.9</v>
@@ -3665,28 +3665,28 @@
         <v>32.9</v>
       </c>
       <c r="M29">
-        <v>2.8489482</v>
+        <v>2.9544648</v>
       </c>
       <c r="N29">
-        <v>30.0510518</v>
+        <v>29.9455352</v>
       </c>
       <c r="O29">
-        <v>10.51786813</v>
+        <v>10.48093732</v>
       </c>
       <c r="P29">
-        <v>19.53318367</v>
+        <v>19.46459788</v>
       </c>
       <c r="Q29">
-        <v>24.43318367</v>
+        <v>24.36459788</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2782149804533223</v>
+        <v>0.2805321431211955</v>
       </c>
       <c r="T29">
-        <v>1.141941300376588</v>
+        <v>1.153326382977435</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.54812151375725</v>
+        <v>11.13568860255164</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2114107430472607</v>
+        <v>0.2106336503635962</v>
       </c>
       <c r="C30">
-        <v>171.7486444337207</v>
+        <v>170.7199833983133</v>
       </c>
       <c r="D30">
-        <v>213.8846444337207</v>
+        <v>214.8929833983133</v>
       </c>
       <c r="E30">
-        <v>42.536</v>
+        <v>44.573</v>
       </c>
       <c r="F30">
-        <v>57.036</v>
+        <v>59.073</v>
       </c>
       <c r="G30">
         <v>14.9</v>
@@ -3747,28 +3747,28 @@
         <v>32.9</v>
       </c>
       <c r="M30">
-        <v>2.9544648</v>
+        <v>3.0599814</v>
       </c>
       <c r="N30">
-        <v>29.9455352</v>
+        <v>29.8400186</v>
       </c>
       <c r="O30">
-        <v>10.48093732</v>
+        <v>10.44400651</v>
       </c>
       <c r="P30">
-        <v>19.46459788</v>
+        <v>19.39601209</v>
       </c>
       <c r="Q30">
-        <v>24.36459788</v>
+        <v>24.29601209</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2805321431211955</v>
+        <v>0.2829145779768961</v>
       </c>
       <c r="T30">
-        <v>1.153326382977435</v>
+        <v>1.165032172130418</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.13568860255164</v>
+        <v>10.75169934039468</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2106336503635962</v>
+        <v>0.2098565576799317</v>
       </c>
       <c r="C31">
-        <v>170.7199833983133</v>
+        <v>169.7008748348474</v>
       </c>
       <c r="D31">
-        <v>214.8929833983133</v>
+        <v>215.9108748348474</v>
       </c>
       <c r="E31">
-        <v>44.57299999999999</v>
+        <v>46.60999999999999</v>
       </c>
       <c r="F31">
-        <v>59.07299999999999</v>
+        <v>61.10999999999999</v>
       </c>
       <c r="G31">
         <v>14.9</v>
@@ -3829,28 +3829,28 @@
         <v>32.9</v>
       </c>
       <c r="M31">
-        <v>3.059981399999999</v>
+        <v>3.165497999999999</v>
       </c>
       <c r="N31">
-        <v>29.8400186</v>
+        <v>29.734502</v>
       </c>
       <c r="O31">
-        <v>10.44400651</v>
+        <v>10.4070757</v>
       </c>
       <c r="P31">
-        <v>19.39601209</v>
+        <v>19.3274263</v>
       </c>
       <c r="Q31">
-        <v>24.29601209</v>
+        <v>24.2274263</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2829145779768961</v>
+        <v>0.2853650823999024</v>
       </c>
       <c r="T31">
-        <v>1.165032172130418</v>
+        <v>1.177072412402057</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.75169934039469</v>
+        <v>10.39330936238153</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2098565576799317</v>
+        <v>0.2090794649962671</v>
       </c>
       <c r="C32">
-        <v>169.7008748348474</v>
+        <v>168.6914551319878</v>
       </c>
       <c r="D32">
-        <v>215.9108748348474</v>
+        <v>216.9384551319878</v>
       </c>
       <c r="E32">
-        <v>46.60999999999999</v>
+        <v>48.647</v>
       </c>
       <c r="F32">
-        <v>61.10999999999999</v>
+        <v>63.147</v>
       </c>
       <c r="G32">
         <v>14.9</v>
@@ -3911,28 +3911,28 @@
         <v>32.9</v>
       </c>
       <c r="M32">
-        <v>3.165497999999999</v>
+        <v>3.2710146</v>
       </c>
       <c r="N32">
-        <v>29.734502</v>
+        <v>29.6289854</v>
       </c>
       <c r="O32">
-        <v>10.4070757</v>
+        <v>10.37014489</v>
       </c>
       <c r="P32">
-        <v>19.3274263</v>
+        <v>19.25884051</v>
       </c>
       <c r="Q32">
-        <v>24.2274263</v>
+        <v>24.15884051</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2853650823999024</v>
+        <v>0.287886615936619</v>
       </c>
       <c r="T32">
-        <v>1.177072412402057</v>
+        <v>1.189461645145338</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.39330936238153</v>
+        <v>10.05804131843374</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2090794649962671</v>
+        <v>0.2086559723126026</v>
       </c>
       <c r="C33">
-        <v>168.6914551319878</v>
+        <v>167.2185845725558</v>
       </c>
       <c r="D33">
-        <v>216.9384551319878</v>
+        <v>217.5025845725558</v>
       </c>
       <c r="E33">
-        <v>48.647</v>
+        <v>50.684</v>
       </c>
       <c r="F33">
-        <v>63.147</v>
+        <v>65.184</v>
       </c>
       <c r="G33">
         <v>14.9</v>
@@ -3993,45 +3993,45 @@
         <v>32.9</v>
       </c>
       <c r="M33">
-        <v>3.2710146</v>
+        <v>3.487344</v>
       </c>
       <c r="N33">
-        <v>29.6289854</v>
+        <v>29.412656</v>
       </c>
       <c r="O33">
-        <v>10.37014489</v>
+        <v>10.2944296</v>
       </c>
       <c r="P33">
-        <v>19.25884051</v>
+        <v>19.1182264</v>
       </c>
       <c r="Q33">
-        <v>24.15884051</v>
+        <v>24.0182264</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.287886615936619</v>
+        <v>0.2904823122244156</v>
       </c>
       <c r="T33">
-        <v>1.189461645145338</v>
+        <v>1.202215267086951</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>10.05804131843374</v>
+        <v>9.434113755339308</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2086559723126026</v>
+        <v>0.207889929628938</v>
       </c>
       <c r="C34">
-        <v>167.2185845725558</v>
+        <v>166.2095094039834</v>
       </c>
       <c r="D34">
-        <v>217.5025845725558</v>
+        <v>218.5305094039834</v>
       </c>
       <c r="E34">
-        <v>50.684</v>
+        <v>52.721</v>
       </c>
       <c r="F34">
-        <v>65.184</v>
+        <v>67.221</v>
       </c>
       <c r="G34">
         <v>14.9</v>
@@ -4075,28 +4075,28 @@
         <v>32.9</v>
       </c>
       <c r="M34">
-        <v>3.487344</v>
+        <v>3.5963235</v>
       </c>
       <c r="N34">
-        <v>29.412656</v>
+        <v>29.3036765</v>
       </c>
       <c r="O34">
-        <v>10.2944296</v>
+        <v>10.256286775</v>
       </c>
       <c r="P34">
-        <v>19.1182264</v>
+        <v>19.047389725</v>
       </c>
       <c r="Q34">
-        <v>24.0182264</v>
+        <v>23.947389725</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2904823122244156</v>
+        <v>0.2931554919834896</v>
       </c>
       <c r="T34">
-        <v>1.202215267086951</v>
+        <v>1.21534959416115</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.434113755339308</v>
+        <v>9.148231520329025</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.207889929628938</v>
+        <v>0.2071238869452735</v>
       </c>
       <c r="C35">
-        <v>166.2095094039834</v>
+        <v>165.2101963891922</v>
       </c>
       <c r="D35">
-        <v>218.5305094039834</v>
+        <v>219.5681963891922</v>
       </c>
       <c r="E35">
-        <v>52.721</v>
+        <v>54.758</v>
       </c>
       <c r="F35">
-        <v>67.221</v>
+        <v>69.258</v>
       </c>
       <c r="G35">
         <v>14.9</v>
@@ -4157,28 +4157,28 @@
         <v>32.9</v>
       </c>
       <c r="M35">
-        <v>3.5963235</v>
+        <v>3.705303</v>
       </c>
       <c r="N35">
-        <v>29.3036765</v>
+        <v>29.194697</v>
       </c>
       <c r="O35">
-        <v>10.256286775</v>
+        <v>10.21814395</v>
       </c>
       <c r="P35">
-        <v>19.047389725</v>
+        <v>18.97655305</v>
       </c>
       <c r="Q35">
-        <v>23.947389725</v>
+        <v>23.87655305</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2931554919834896</v>
+        <v>0.2959096771898084</v>
       </c>
       <c r="T35">
-        <v>1.21534959416115</v>
+        <v>1.228881931146688</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.148231520329025</v>
+        <v>8.879165887378171</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2071238869452735</v>
+        <v>0.2063578442616089</v>
       </c>
       <c r="C36">
-        <v>165.2101963891922</v>
+        <v>164.2207852577579</v>
       </c>
       <c r="D36">
-        <v>219.5681963891922</v>
+        <v>220.6157852577579</v>
       </c>
       <c r="E36">
-        <v>54.758</v>
+        <v>56.795</v>
       </c>
       <c r="F36">
-        <v>69.258</v>
+        <v>71.295</v>
       </c>
       <c r="G36">
         <v>14.9</v>
@@ -4239,28 +4239,28 @@
         <v>32.9</v>
       </c>
       <c r="M36">
-        <v>3.705303</v>
+        <v>3.8142825</v>
       </c>
       <c r="N36">
-        <v>29.194697</v>
+        <v>29.0857175</v>
       </c>
       <c r="O36">
-        <v>10.21814395</v>
+        <v>10.180001125</v>
       </c>
       <c r="P36">
-        <v>18.97655305</v>
+        <v>18.905716375</v>
       </c>
       <c r="Q36">
-        <v>23.87655305</v>
+        <v>23.805716375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2959096771898084</v>
+        <v>0.2987486065563215</v>
       </c>
       <c r="T36">
-        <v>1.228881931146688</v>
+        <v>1.242830647731781</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.879165887378171</v>
+        <v>8.625475433453079</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2063578442616089</v>
+        <v>0.2055918015779445</v>
       </c>
       <c r="C37">
-        <v>164.2207852577579</v>
+        <v>163.241418418713</v>
       </c>
       <c r="D37">
-        <v>220.6157852577579</v>
+        <v>221.673418418713</v>
       </c>
       <c r="E37">
-        <v>56.795</v>
+        <v>58.83200000000001</v>
       </c>
       <c r="F37">
-        <v>71.295</v>
+        <v>73.33200000000001</v>
       </c>
       <c r="G37">
         <v>14.9</v>
@@ -4321,28 +4321,28 @@
         <v>32.9</v>
       </c>
       <c r="M37">
-        <v>3.8142825</v>
+        <v>3.923262</v>
       </c>
       <c r="N37">
-        <v>29.0857175</v>
+        <v>28.976738</v>
       </c>
       <c r="O37">
-        <v>10.180001125</v>
+        <v>10.1418583</v>
       </c>
       <c r="P37">
-        <v>18.905716375</v>
+        <v>18.8348797</v>
       </c>
       <c r="Q37">
-        <v>23.805716375</v>
+        <v>23.7348797</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2987486065563215</v>
+        <v>0.3016762524655383</v>
       </c>
       <c r="T37">
-        <v>1.242830647731781</v>
+        <v>1.257215261710158</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.625475433453079</v>
+        <v>8.385878893634938</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2055918015779445</v>
+        <v>0.2048257588942799</v>
       </c>
       <c r="C38">
-        <v>163.241418418713</v>
+        <v>162.2722410250837</v>
       </c>
       <c r="D38">
-        <v>221.673418418713</v>
+        <v>222.7412410250837</v>
       </c>
       <c r="E38">
-        <v>58.83199999999999</v>
+        <v>60.869</v>
       </c>
       <c r="F38">
-        <v>73.33199999999999</v>
+        <v>75.369</v>
       </c>
       <c r="G38">
         <v>14.9</v>
@@ -4403,28 +4403,28 @@
         <v>32.9</v>
       </c>
       <c r="M38">
-        <v>3.923261999999999</v>
+        <v>4.0322415</v>
       </c>
       <c r="N38">
-        <v>28.976738</v>
+        <v>28.8677585</v>
       </c>
       <c r="O38">
-        <v>10.1418583</v>
+        <v>10.103715475</v>
       </c>
       <c r="P38">
-        <v>18.8348797</v>
+        <v>18.764043025</v>
       </c>
       <c r="Q38">
-        <v>23.7348797</v>
+        <v>23.664043025</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3016762524655383</v>
+        <v>0.30469683951473</v>
       </c>
       <c r="T38">
-        <v>1.257215261710158</v>
+        <v>1.272056530100547</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.38587889363494</v>
+        <v>8.159233518131295</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2048257588942799</v>
+        <v>0.2040597162106154</v>
       </c>
       <c r="C39">
-        <v>162.2722410250837</v>
+        <v>161.3134010402991</v>
       </c>
       <c r="D39">
-        <v>222.7412410250837</v>
+        <v>223.8194010402991</v>
       </c>
       <c r="E39">
-        <v>60.869</v>
+        <v>62.90599999999999</v>
       </c>
       <c r="F39">
-        <v>75.369</v>
+        <v>77.40599999999999</v>
       </c>
       <c r="G39">
         <v>14.9</v>
@@ -4485,28 +4485,28 @@
         <v>32.9</v>
       </c>
       <c r="M39">
-        <v>4.0322415</v>
+        <v>4.141221</v>
       </c>
       <c r="N39">
-        <v>28.8677585</v>
+        <v>28.758779</v>
       </c>
       <c r="O39">
-        <v>10.103715475</v>
+        <v>10.06557265</v>
       </c>
       <c r="P39">
-        <v>18.764043025</v>
+        <v>18.69320635</v>
       </c>
       <c r="Q39">
-        <v>23.664043025</v>
+        <v>23.59320635</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.30469683951473</v>
+        <v>0.3078148648558313</v>
       </c>
       <c r="T39">
-        <v>1.272056530100547</v>
+        <v>1.287376549084174</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.159233518131295</v>
+        <v>7.944516846601521</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2040597162106154</v>
+        <v>0.2032936735269508</v>
       </c>
       <c r="C40">
-        <v>161.3134010402991</v>
+        <v>160.3650493065405</v>
       </c>
       <c r="D40">
-        <v>223.8194010402991</v>
+        <v>224.9080493065405</v>
       </c>
       <c r="E40">
-        <v>62.90599999999999</v>
+        <v>64.943</v>
       </c>
       <c r="F40">
-        <v>77.40599999999999</v>
+        <v>79.443</v>
       </c>
       <c r="G40">
         <v>14.9</v>
@@ -4567,28 +4567,28 @@
         <v>32.9</v>
       </c>
       <c r="M40">
-        <v>4.141221</v>
+        <v>4.2502005</v>
       </c>
       <c r="N40">
-        <v>28.758779</v>
+        <v>28.6497995</v>
       </c>
       <c r="O40">
-        <v>10.06557265</v>
+        <v>10.027429825</v>
       </c>
       <c r="P40">
-        <v>18.69320635</v>
+        <v>18.622369675</v>
       </c>
       <c r="Q40">
-        <v>23.59320635</v>
+        <v>23.522369675</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3078148648558313</v>
+        <v>0.311035120535985</v>
       </c>
       <c r="T40">
-        <v>1.287376549084174</v>
+        <v>1.303198863772183</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.944516846601521</v>
+        <v>7.740811286432252</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2032936735269508</v>
+        <v>0.2027356308432863</v>
       </c>
       <c r="C41">
-        <v>160.3650493065405</v>
+        <v>159.1277930660575</v>
       </c>
       <c r="D41">
-        <v>224.9080493065405</v>
+        <v>225.7077930660575</v>
       </c>
       <c r="E41">
-        <v>64.943</v>
+        <v>66.98</v>
       </c>
       <c r="F41">
-        <v>79.443</v>
+        <v>81.48</v>
       </c>
       <c r="G41">
         <v>14.9</v>
@@ -4649,45 +4649,45 @@
         <v>32.9</v>
       </c>
       <c r="M41">
-        <v>4.2502005</v>
+        <v>4.424364000000001</v>
       </c>
       <c r="N41">
-        <v>28.6497995</v>
+        <v>28.475636</v>
       </c>
       <c r="O41">
-        <v>10.027429825</v>
+        <v>9.966472599999999</v>
       </c>
       <c r="P41">
-        <v>18.622369675</v>
+        <v>18.5091634</v>
       </c>
       <c r="Q41">
-        <v>23.522369675</v>
+        <v>23.4091634</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.311035120535985</v>
+        <v>0.3143627180721438</v>
       </c>
       <c r="T41">
-        <v>1.303198863772183</v>
+        <v>1.319548588949792</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.35</v>
       </c>
       <c r="W41">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.740811286432252</v>
+        <v>7.436097029991202</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2027356308432863</v>
+        <v>0.2019747881596218</v>
       </c>
       <c r="C42">
-        <v>159.1277930660575</v>
+        <v>158.1903823469141</v>
       </c>
       <c r="D42">
-        <v>225.7077930660575</v>
+        <v>226.8073823469141</v>
       </c>
       <c r="E42">
-        <v>66.98</v>
+        <v>69.017</v>
       </c>
       <c r="F42">
-        <v>81.48</v>
+        <v>83.517</v>
       </c>
       <c r="G42">
         <v>14.9</v>
@@ -4731,28 +4731,28 @@
         <v>32.9</v>
       </c>
       <c r="M42">
-        <v>4.424364000000001</v>
+        <v>4.5349731</v>
       </c>
       <c r="N42">
-        <v>28.475636</v>
+        <v>28.3650269</v>
       </c>
       <c r="O42">
-        <v>9.966472599999999</v>
+        <v>9.927759414999999</v>
       </c>
       <c r="P42">
-        <v>18.5091634</v>
+        <v>18.437267485</v>
       </c>
       <c r="Q42">
-        <v>23.4091634</v>
+        <v>23.337267485</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3143627180721438</v>
+        <v>0.3178031155247827</v>
       </c>
       <c r="T42">
-        <v>1.319548588949792</v>
+        <v>1.336452542099523</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.436097029991202</v>
+        <v>7.254728809747514</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2019747881596218</v>
+        <v>0.2012139454759572</v>
       </c>
       <c r="C43">
-        <v>158.1903823469141</v>
+        <v>157.2637379004732</v>
       </c>
       <c r="D43">
-        <v>226.8073823469141</v>
+        <v>227.9177379004732</v>
       </c>
       <c r="E43">
-        <v>69.017</v>
+        <v>71.054</v>
       </c>
       <c r="F43">
-        <v>83.517</v>
+        <v>85.554</v>
       </c>
       <c r="G43">
         <v>14.9</v>
@@ -4813,28 +4813,28 @@
         <v>32.9</v>
       </c>
       <c r="M43">
-        <v>4.5349731</v>
+        <v>4.6455822</v>
       </c>
       <c r="N43">
-        <v>28.3650269</v>
+        <v>28.2544178</v>
       </c>
       <c r="O43">
-        <v>9.927759414999999</v>
+        <v>9.889046229999998</v>
       </c>
       <c r="P43">
-        <v>18.437267485</v>
+        <v>18.36537157</v>
       </c>
       <c r="Q43">
-        <v>23.337267485</v>
+        <v>23.26537157</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3178031155247827</v>
+        <v>0.32136214737234</v>
       </c>
       <c r="T43">
-        <v>1.336452542099523</v>
+        <v>1.353939390185452</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.254728809747514</v>
+        <v>7.081997171420194</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2012139454759573</v>
+        <v>0.2004531027922927</v>
       </c>
       <c r="C44">
-        <v>157.2637379004732</v>
+        <v>156.3480186263558</v>
       </c>
       <c r="D44">
-        <v>227.9177379004732</v>
+        <v>229.0390186263558</v>
       </c>
       <c r="E44">
-        <v>71.05399999999999</v>
+        <v>73.09099999999999</v>
       </c>
       <c r="F44">
-        <v>85.55399999999999</v>
+        <v>87.59099999999999</v>
       </c>
       <c r="G44">
         <v>14.9</v>
@@ -4895,28 +4895,28 @@
         <v>32.9</v>
       </c>
       <c r="M44">
-        <v>4.6455822</v>
+        <v>4.756191299999999</v>
       </c>
       <c r="N44">
-        <v>28.2544178</v>
+        <v>28.1438087</v>
       </c>
       <c r="O44">
-        <v>9.889046229999998</v>
+        <v>9.850333044999999</v>
       </c>
       <c r="P44">
-        <v>18.36537157</v>
+        <v>18.293475655</v>
       </c>
       <c r="Q44">
-        <v>23.26537157</v>
+        <v>23.193475655</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.32136214737234</v>
+        <v>0.3250460575303381</v>
       </c>
       <c r="T44">
-        <v>1.353939390185452</v>
+        <v>1.372039811888431</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.081997171420194</v>
+        <v>6.917299562782516</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2004531027922927</v>
+        <v>0.1996922601086281</v>
       </c>
       <c r="C45">
-        <v>156.3480186263558</v>
+        <v>155.4433865665795</v>
       </c>
       <c r="D45">
-        <v>229.0390186263558</v>
+        <v>230.1713865665795</v>
       </c>
       <c r="E45">
-        <v>73.09099999999999</v>
+        <v>75.128</v>
       </c>
       <c r="F45">
-        <v>87.59099999999999</v>
+        <v>89.628</v>
       </c>
       <c r="G45">
         <v>14.9</v>
@@ -4977,28 +4977,28 @@
         <v>32.9</v>
       </c>
       <c r="M45">
-        <v>4.756191299999999</v>
+        <v>4.8668004</v>
       </c>
       <c r="N45">
-        <v>28.1438087</v>
+        <v>28.0331996</v>
       </c>
       <c r="O45">
-        <v>9.850333044999999</v>
+        <v>9.811619859999999</v>
       </c>
       <c r="P45">
-        <v>18.293475655</v>
+        <v>18.22157974</v>
       </c>
       <c r="Q45">
-        <v>23.193475655</v>
+        <v>23.12157974</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3250460575303381</v>
+        <v>0.3288615359082645</v>
       </c>
       <c r="T45">
-        <v>1.372039811888431</v>
+        <v>1.390786677223659</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.917299562782516</v>
+        <v>6.760088209082912</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1996922601086281</v>
+        <v>0.1989314174249636</v>
       </c>
       <c r="C46">
-        <v>155.4433865665795</v>
+        <v>154.5500069836237</v>
       </c>
       <c r="D46">
-        <v>230.1713865665795</v>
+        <v>231.3150069836237</v>
       </c>
       <c r="E46">
-        <v>75.128</v>
+        <v>77.16499999999999</v>
       </c>
       <c r="F46">
-        <v>89.628</v>
+        <v>91.66499999999999</v>
       </c>
       <c r="G46">
         <v>14.9</v>
@@ -5059,28 +5059,28 @@
         <v>32.9</v>
       </c>
       <c r="M46">
-        <v>4.8668004</v>
+        <v>4.977409499999999</v>
       </c>
       <c r="N46">
-        <v>28.0331996</v>
+        <v>27.9225905</v>
       </c>
       <c r="O46">
-        <v>9.811619859999999</v>
+        <v>9.772906674999998</v>
       </c>
       <c r="P46">
-        <v>18.22157974</v>
+        <v>18.149683825</v>
       </c>
       <c r="Q46">
-        <v>23.12157974</v>
+        <v>23.049683825</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3288615359082645</v>
+        <v>0.3328157589544793</v>
       </c>
       <c r="T46">
-        <v>1.390786677223659</v>
+        <v>1.410215246752896</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.760088209082912</v>
+        <v>6.609864026658848</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1989314174249636</v>
+        <v>0.1981705747412991</v>
       </c>
       <c r="C47">
-        <v>154.5500069836237</v>
+        <v>153.6680484408349</v>
       </c>
       <c r="D47">
-        <v>231.3150069836237</v>
+        <v>232.4700484408349</v>
       </c>
       <c r="E47">
-        <v>77.16499999999999</v>
+        <v>79.202</v>
       </c>
       <c r="F47">
-        <v>91.66499999999999</v>
+        <v>93.702</v>
       </c>
       <c r="G47">
         <v>14.9</v>
@@ -5141,28 +5141,28 @@
         <v>32.9</v>
       </c>
       <c r="M47">
-        <v>4.977409499999999</v>
+        <v>5.0880186</v>
       </c>
       <c r="N47">
-        <v>27.9225905</v>
+        <v>27.8119814</v>
       </c>
       <c r="O47">
-        <v>9.772906674999998</v>
+        <v>9.734193489999999</v>
       </c>
       <c r="P47">
-        <v>18.149683825</v>
+        <v>18.07778791</v>
       </c>
       <c r="Q47">
-        <v>23.049683825</v>
+        <v>22.97778791</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3328157589544793</v>
+        <v>0.3369164347061094</v>
       </c>
       <c r="T47">
-        <v>1.410215246752896</v>
+        <v>1.430363392931364</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.609864026658848</v>
+        <v>6.466171330427134</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1981705747412991</v>
+        <v>0.1974097320576346</v>
       </c>
       <c r="C48">
-        <v>153.6680484408349</v>
+        <v>152.7976828852524</v>
       </c>
       <c r="D48">
-        <v>232.4700484408349</v>
+        <v>233.6366828852524</v>
       </c>
       <c r="E48">
-        <v>79.202</v>
+        <v>81.239</v>
       </c>
       <c r="F48">
-        <v>93.702</v>
+        <v>95.739</v>
       </c>
       <c r="G48">
         <v>14.9</v>
@@ -5223,28 +5223,28 @@
         <v>32.9</v>
       </c>
       <c r="M48">
-        <v>5.0880186</v>
+        <v>5.1986277</v>
       </c>
       <c r="N48">
-        <v>27.8119814</v>
+        <v>27.7013723</v>
       </c>
       <c r="O48">
-        <v>9.734193489999999</v>
+        <v>9.695480304999998</v>
       </c>
       <c r="P48">
-        <v>18.07778791</v>
+        <v>18.005891995</v>
       </c>
       <c r="Q48">
-        <v>22.97778791</v>
+        <v>22.905891995</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3369164347061094</v>
+        <v>0.3411718529389331</v>
       </c>
       <c r="T48">
-        <v>1.430363392931364</v>
+        <v>1.451271846512793</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.466171330427134</v>
+        <v>6.32859321701379</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1974097320576346</v>
+        <v>0.19664888937397</v>
       </c>
       <c r="C49">
-        <v>152.7976828852524</v>
+        <v>151.9390857329407</v>
       </c>
       <c r="D49">
-        <v>233.6366828852524</v>
+        <v>234.8150857329407</v>
       </c>
       <c r="E49">
-        <v>81.239</v>
+        <v>83.276</v>
       </c>
       <c r="F49">
-        <v>95.739</v>
+        <v>97.776</v>
       </c>
       <c r="G49">
         <v>14.9</v>
@@ -5305,28 +5305,28 @@
         <v>32.9</v>
       </c>
       <c r="M49">
-        <v>5.1986277</v>
+        <v>5.3092368</v>
       </c>
       <c r="N49">
-        <v>27.7013723</v>
+        <v>27.5907632</v>
       </c>
       <c r="O49">
-        <v>9.695480304999998</v>
+        <v>9.656767119999998</v>
       </c>
       <c r="P49">
-        <v>18.005891995</v>
+        <v>17.93399608</v>
       </c>
       <c r="Q49">
-        <v>22.905891995</v>
+        <v>22.83399608</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3411718529389331</v>
+        <v>0.3455909411037885</v>
       </c>
       <c r="T49">
-        <v>1.451271846512793</v>
+        <v>1.472984471385814</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.32859321701379</v>
+        <v>6.196747524992669</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.19664888937397</v>
+        <v>0.1962065466903055</v>
       </c>
       <c r="C50">
-        <v>151.9390857329407</v>
+        <v>150.5926722630729</v>
       </c>
       <c r="D50">
-        <v>234.8150857329407</v>
+        <v>235.5056722630729</v>
       </c>
       <c r="E50">
-        <v>83.276</v>
+        <v>85.31299999999999</v>
       </c>
       <c r="F50">
-        <v>97.776</v>
+        <v>99.81299999999999</v>
       </c>
       <c r="G50">
         <v>14.9</v>
@@ -5387,45 +5387,45 @@
         <v>32.9</v>
       </c>
       <c r="M50">
-        <v>5.3092368</v>
+        <v>5.5196589</v>
       </c>
       <c r="N50">
-        <v>27.5907632</v>
+        <v>27.3803411</v>
       </c>
       <c r="O50">
-        <v>9.656767119999998</v>
+        <v>9.583119385</v>
       </c>
       <c r="P50">
-        <v>17.93399608</v>
+        <v>17.797221715</v>
       </c>
       <c r="Q50">
-        <v>22.83399608</v>
+        <v>22.697221715</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3455909411037885</v>
+        <v>0.3501833268437362</v>
       </c>
       <c r="T50">
-        <v>1.472984471385814</v>
+        <v>1.495548571744053</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.196747524992669</v>
+        <v>5.960513248382069</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1962065466903055</v>
+        <v>0.1954522040066409</v>
       </c>
       <c r="C51">
-        <v>150.5926722630729</v>
+        <v>149.7427712571196</v>
       </c>
       <c r="D51">
-        <v>235.5056722630729</v>
+        <v>236.6927712571196</v>
       </c>
       <c r="E51">
-        <v>85.31299999999999</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="F51">
-        <v>99.81299999999999</v>
+        <v>101.85</v>
       </c>
       <c r="G51">
         <v>14.9</v>
@@ -5469,28 +5469,28 @@
         <v>32.9</v>
       </c>
       <c r="M51">
-        <v>5.5196589</v>
+        <v>5.632305</v>
       </c>
       <c r="N51">
-        <v>27.3803411</v>
+        <v>27.267695</v>
       </c>
       <c r="O51">
-        <v>9.583119385</v>
+        <v>9.543693249999999</v>
       </c>
       <c r="P51">
-        <v>17.797221715</v>
+        <v>17.72400175</v>
       </c>
       <c r="Q51">
-        <v>22.697221715</v>
+        <v>22.62400175</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3501833268437362</v>
+        <v>0.3549594080132818</v>
       </c>
       <c r="T51">
-        <v>1.495548571744053</v>
+        <v>1.519015236116621</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.960513248382069</v>
+        <v>5.841302983414428</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1954522040066409</v>
+        <v>0.1946978613229764</v>
       </c>
       <c r="C52">
-        <v>149.7427712571196</v>
+        <v>148.9048983546324</v>
       </c>
       <c r="D52">
-        <v>236.6927712571196</v>
+        <v>237.8918983546324</v>
       </c>
       <c r="E52">
-        <v>87.34999999999999</v>
+        <v>89.387</v>
       </c>
       <c r="F52">
-        <v>101.85</v>
+        <v>103.887</v>
       </c>
       <c r="G52">
         <v>14.9</v>
@@ -5551,28 +5551,28 @@
         <v>32.9</v>
       </c>
       <c r="M52">
-        <v>5.632305</v>
+        <v>5.744951100000001</v>
       </c>
       <c r="N52">
-        <v>27.267695</v>
+        <v>27.1550489</v>
       </c>
       <c r="O52">
-        <v>9.543693249999999</v>
+        <v>9.504267114999998</v>
       </c>
       <c r="P52">
-        <v>17.72400175</v>
+        <v>17.650781785</v>
       </c>
       <c r="Q52">
-        <v>22.62400175</v>
+        <v>22.550781785</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3549594080132818</v>
+        <v>0.3599304312713804</v>
       </c>
       <c r="T52">
-        <v>1.519015236116621</v>
+        <v>1.543439723524804</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.841302983414428</v>
+        <v>5.726767630798458</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1946978613229764</v>
+        <v>0.1939435186393118</v>
       </c>
       <c r="C53">
-        <v>148.9048983546324</v>
+        <v>148.0792372959181</v>
       </c>
       <c r="D53">
-        <v>237.8918983546324</v>
+        <v>239.1032372959181</v>
       </c>
       <c r="E53">
-        <v>89.387</v>
+        <v>91.42399999999999</v>
       </c>
       <c r="F53">
-        <v>103.887</v>
+        <v>105.924</v>
       </c>
       <c r="G53">
         <v>14.9</v>
@@ -5633,28 +5633,28 @@
         <v>32.9</v>
       </c>
       <c r="M53">
-        <v>5.744951100000001</v>
+        <v>5.8575972</v>
       </c>
       <c r="N53">
-        <v>27.1550489</v>
+        <v>27.0424028</v>
       </c>
       <c r="O53">
-        <v>9.504267114999998</v>
+        <v>9.464840979999998</v>
       </c>
       <c r="P53">
-        <v>17.650781785</v>
+        <v>17.57756182</v>
       </c>
       <c r="Q53">
-        <v>22.550781785</v>
+        <v>22.47756182</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3599304312713804</v>
+        <v>0.3651085804985664</v>
       </c>
       <c r="T53">
-        <v>1.543439723524804</v>
+        <v>1.568881897908329</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.726767630798458</v>
+        <v>5.616637484052334</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1939435186393118</v>
+        <v>0.1931891759556473</v>
       </c>
       <c r="C54">
-        <v>148.0792372959181</v>
+        <v>147.2659755828393</v>
       </c>
       <c r="D54">
-        <v>239.1032372959181</v>
+        <v>240.3269755828393</v>
       </c>
       <c r="E54">
-        <v>91.42399999999999</v>
+        <v>93.461</v>
       </c>
       <c r="F54">
-        <v>105.924</v>
+        <v>107.961</v>
       </c>
       <c r="G54">
         <v>14.9</v>
@@ -5715,28 +5715,28 @@
         <v>32.9</v>
       </c>
       <c r="M54">
-        <v>5.8575972</v>
+        <v>5.9702433</v>
       </c>
       <c r="N54">
-        <v>27.0424028</v>
+        <v>26.9297567</v>
       </c>
       <c r="O54">
-        <v>9.464840979999998</v>
+        <v>9.425414844999999</v>
       </c>
       <c r="P54">
-        <v>17.57756182</v>
+        <v>17.504341855</v>
       </c>
       <c r="Q54">
-        <v>22.47756182</v>
+        <v>22.404341855</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3651085804985664</v>
+        <v>0.3705070765013773</v>
       </c>
       <c r="T54">
-        <v>1.568881897908329</v>
+        <v>1.5954067180103</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.616637484052334</v>
+        <v>5.510663191900403</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1931891759556473</v>
+        <v>0.1924348332719828</v>
       </c>
       <c r="C55">
-        <v>147.2659755828393</v>
+        <v>146.4653045755683</v>
       </c>
       <c r="D55">
-        <v>240.3269755828393</v>
+        <v>241.5633045755683</v>
       </c>
       <c r="E55">
-        <v>93.461</v>
+        <v>95.498</v>
       </c>
       <c r="F55">
-        <v>107.961</v>
+        <v>109.998</v>
       </c>
       <c r="G55">
         <v>14.9</v>
@@ -5797,28 +5797,28 @@
         <v>32.9</v>
       </c>
       <c r="M55">
-        <v>5.9702433</v>
+        <v>6.082889400000001</v>
       </c>
       <c r="N55">
-        <v>26.9297567</v>
+        <v>26.8171106</v>
       </c>
       <c r="O55">
-        <v>9.425414844999999</v>
+        <v>9.385988709999999</v>
       </c>
       <c r="P55">
-        <v>17.504341855</v>
+        <v>17.43112189</v>
       </c>
       <c r="Q55">
-        <v>22.404341855</v>
+        <v>22.33112189</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3705070765013773</v>
+        <v>0.3761402897217017</v>
       </c>
       <c r="T55">
-        <v>1.5954067180103</v>
+        <v>1.623084791160184</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.510663191900403</v>
+        <v>5.408613873531877</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1924348332719828</v>
+        <v>0.1916804905883182</v>
       </c>
       <c r="C56">
-        <v>146.4653045755683</v>
+        <v>145.6774195923436</v>
       </c>
       <c r="D56">
-        <v>241.5633045755683</v>
+        <v>242.8124195923436</v>
       </c>
       <c r="E56">
-        <v>95.498</v>
+        <v>97.535</v>
       </c>
       <c r="F56">
-        <v>109.998</v>
+        <v>112.035</v>
       </c>
       <c r="G56">
         <v>14.9</v>
@@ -5879,28 +5879,28 @@
         <v>32.9</v>
       </c>
       <c r="M56">
-        <v>6.082889400000001</v>
+        <v>6.1955355</v>
       </c>
       <c r="N56">
-        <v>26.8171106</v>
+        <v>26.7044645</v>
       </c>
       <c r="O56">
-        <v>9.385988709999999</v>
+        <v>9.346562575</v>
       </c>
       <c r="P56">
-        <v>17.43112189</v>
+        <v>17.357901925</v>
       </c>
       <c r="Q56">
-        <v>22.33112189</v>
+        <v>22.257901925</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3761402897217017</v>
+        <v>0.3820238679740406</v>
       </c>
       <c r="T56">
-        <v>1.623084791160184</v>
+        <v>1.651993000894507</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.408613873531877</v>
+        <v>5.310275439467662</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1916804905883182</v>
+        <v>0.1909261479046537</v>
       </c>
       <c r="C57">
-        <v>145.6774195923436</v>
+        <v>144.9025200123361</v>
       </c>
       <c r="D57">
-        <v>242.8124195923436</v>
+        <v>244.0745200123361</v>
       </c>
       <c r="E57">
-        <v>97.535</v>
+        <v>99.572</v>
       </c>
       <c r="F57">
-        <v>112.035</v>
+        <v>114.072</v>
       </c>
       <c r="G57">
         <v>14.9</v>
@@ -5961,28 +5961,28 @@
         <v>32.9</v>
       </c>
       <c r="M57">
-        <v>6.1955355</v>
+        <v>6.3081816</v>
       </c>
       <c r="N57">
-        <v>26.7044645</v>
+        <v>26.5918184</v>
       </c>
       <c r="O57">
-        <v>9.346562575</v>
+        <v>9.307136439999999</v>
       </c>
       <c r="P57">
-        <v>17.357901925</v>
+        <v>17.28468196</v>
       </c>
       <c r="Q57">
-        <v>22.257901925</v>
+        <v>22.18468196</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3820238679740406</v>
+        <v>0.3881748816014857</v>
       </c>
       <c r="T57">
-        <v>1.651993000894507</v>
+        <v>1.682215220162209</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.310275439467662</v>
+        <v>5.21544909233431</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1909261479046537</v>
+        <v>0.1901718052209891</v>
       </c>
       <c r="C58">
-        <v>144.9025200123361</v>
+        <v>144.1408093817418</v>
       </c>
       <c r="D58">
-        <v>244.0745200123361</v>
+        <v>245.3498093817418</v>
       </c>
       <c r="E58">
-        <v>99.572</v>
+        <v>101.609</v>
       </c>
       <c r="F58">
-        <v>114.072</v>
+        <v>116.109</v>
       </c>
       <c r="G58">
         <v>14.9</v>
@@ -6043,28 +6043,28 @@
         <v>32.9</v>
       </c>
       <c r="M58">
-        <v>6.3081816</v>
+        <v>6.420827700000001</v>
       </c>
       <c r="N58">
-        <v>26.5918184</v>
+        <v>26.4791723</v>
       </c>
       <c r="O58">
-        <v>9.307136439999999</v>
+        <v>9.267710305</v>
       </c>
       <c r="P58">
-        <v>17.28468196</v>
+        <v>17.211461995</v>
       </c>
       <c r="Q58">
-        <v>22.18468196</v>
+        <v>22.111461995</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3881748816014857</v>
+        <v>0.3946119888860213</v>
       </c>
       <c r="T58">
-        <v>1.682215220162209</v>
+        <v>1.713843124047012</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.21544909233431</v>
+        <v>5.123949985451252</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1901718052209891</v>
+        <v>0.1894174625373246</v>
       </c>
       <c r="C59">
-        <v>144.1408093817418</v>
+        <v>143.3924955232164</v>
       </c>
       <c r="D59">
-        <v>245.3498093817418</v>
+        <v>246.6384955232164</v>
       </c>
       <c r="E59">
-        <v>101.609</v>
+        <v>103.646</v>
       </c>
       <c r="F59">
-        <v>116.109</v>
+        <v>118.146</v>
       </c>
       <c r="G59">
         <v>14.9</v>
@@ -6125,28 +6125,28 @@
         <v>32.9</v>
       </c>
       <c r="M59">
-        <v>6.420827700000001</v>
+        <v>6.5334738</v>
       </c>
       <c r="N59">
-        <v>26.4791723</v>
+        <v>26.3665262</v>
       </c>
       <c r="O59">
-        <v>9.267710305</v>
+        <v>9.228284169999998</v>
       </c>
       <c r="P59">
-        <v>17.211461995</v>
+        <v>17.13824203</v>
       </c>
       <c r="Q59">
-        <v>22.111461995</v>
+        <v>22.03824203</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3946119888860213</v>
+        <v>0.4013556250888682</v>
       </c>
       <c r="T59">
-        <v>1.713843124047012</v>
+        <v>1.746977118592997</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.123949985451252</v>
+        <v>5.035606020184852</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1894174625373246</v>
+        <v>0.1886631198536601</v>
       </c>
       <c r="C60">
-        <v>143.3924955232165</v>
+        <v>142.6577906487782</v>
       </c>
       <c r="D60">
-        <v>246.6384955232164</v>
+        <v>247.9407906487782</v>
       </c>
       <c r="E60">
-        <v>103.646</v>
+        <v>105.683</v>
       </c>
       <c r="F60">
-        <v>118.146</v>
+        <v>120.183</v>
       </c>
       <c r="G60">
         <v>14.9</v>
@@ -6207,28 +6207,28 @@
         <v>32.9</v>
       </c>
       <c r="M60">
-        <v>6.533473799999999</v>
+        <v>6.6461199</v>
       </c>
       <c r="N60">
-        <v>26.3665262</v>
+        <v>26.2538801</v>
       </c>
       <c r="O60">
-        <v>9.228284169999998</v>
+        <v>9.188858034999999</v>
       </c>
       <c r="P60">
-        <v>17.13824203</v>
+        <v>17.065022065</v>
       </c>
       <c r="Q60">
-        <v>22.03824203</v>
+        <v>21.965022065</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4013556250888681</v>
+        <v>0.4084282191552685</v>
       </c>
       <c r="T60">
-        <v>1.746977118592997</v>
+        <v>1.781727405555859</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.035606020184852</v>
+        <v>4.950256765605448</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1886631198536601</v>
+        <v>0.1879087771699955</v>
       </c>
       <c r="C61">
-        <v>142.6577906487782</v>
+        <v>141.9369114763059</v>
       </c>
       <c r="D61">
-        <v>247.9407906487782</v>
+        <v>249.2569114763058</v>
       </c>
       <c r="E61">
-        <v>105.683</v>
+        <v>107.72</v>
       </c>
       <c r="F61">
-        <v>120.183</v>
+        <v>122.22</v>
       </c>
       <c r="G61">
         <v>14.9</v>
@@ -6289,28 +6289,28 @@
         <v>32.9</v>
       </c>
       <c r="M61">
-        <v>6.6461199</v>
+        <v>6.758766</v>
       </c>
       <c r="N61">
-        <v>26.2538801</v>
+        <v>26.141234</v>
       </c>
       <c r="O61">
-        <v>9.188858034999999</v>
+        <v>9.149431899999998</v>
       </c>
       <c r="P61">
-        <v>17.065022065</v>
+        <v>16.9918021</v>
       </c>
       <c r="Q61">
-        <v>21.965022065</v>
+        <v>21.8918021</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4084282191552685</v>
+        <v>0.4158544429249889</v>
       </c>
       <c r="T61">
-        <v>1.781727405555859</v>
+        <v>1.818215206866864</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.950256765605448</v>
+        <v>4.86775248617869</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1879087771699955</v>
+        <v>0.187154434486331</v>
       </c>
       <c r="C62">
-        <v>141.9369114763059</v>
+        <v>141.2300793497668</v>
       </c>
       <c r="D62">
-        <v>249.2569114763058</v>
+        <v>250.5870793497668</v>
       </c>
       <c r="E62">
-        <v>107.72</v>
+        <v>109.757</v>
       </c>
       <c r="F62">
-        <v>122.22</v>
+        <v>124.257</v>
       </c>
       <c r="G62">
         <v>14.9</v>
@@ -6371,28 +6371,28 @@
         <v>32.9</v>
       </c>
       <c r="M62">
-        <v>6.758766</v>
+        <v>6.8714121</v>
       </c>
       <c r="N62">
-        <v>26.141234</v>
+        <v>26.0285879</v>
       </c>
       <c r="O62">
-        <v>9.149431899999998</v>
+        <v>9.110005764999999</v>
       </c>
       <c r="P62">
-        <v>16.9918021</v>
+        <v>16.918582135</v>
       </c>
       <c r="Q62">
-        <v>21.8918021</v>
+        <v>21.818582135</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4158544429249889</v>
+        <v>0.4236614986829</v>
       </c>
       <c r="T62">
-        <v>1.818215206866864</v>
+        <v>1.85657417747587</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.86775248617869</v>
+        <v>4.787953265093794</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.187154434486331</v>
+        <v>0.1864000918026665</v>
       </c>
       <c r="C63">
-        <v>141.2300793497668</v>
+        <v>140.5375203633166</v>
       </c>
       <c r="D63">
-        <v>250.5870793497668</v>
+        <v>251.9315203633166</v>
       </c>
       <c r="E63">
-        <v>109.757</v>
+        <v>111.794</v>
       </c>
       <c r="F63">
-        <v>124.257</v>
+        <v>126.294</v>
       </c>
       <c r="G63">
         <v>14.9</v>
@@ -6453,28 +6453,28 @@
         <v>32.9</v>
       </c>
       <c r="M63">
-        <v>6.8714121</v>
+        <v>6.9840582</v>
       </c>
       <c r="N63">
-        <v>26.0285879</v>
+        <v>25.9159418</v>
       </c>
       <c r="O63">
-        <v>9.110005764999999</v>
+        <v>9.070579629999999</v>
       </c>
       <c r="P63">
-        <v>16.918582135</v>
+        <v>16.84536217</v>
       </c>
       <c r="Q63">
-        <v>21.818582135</v>
+        <v>21.74536217</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4236614986829</v>
+        <v>0.4318794521122802</v>
       </c>
       <c r="T63">
-        <v>1.85657417747587</v>
+        <v>1.896952041274824</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.787953265093794</v>
+        <v>4.71072821243099</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1864000918026665</v>
+        <v>0.1856457491190019</v>
       </c>
       <c r="C64">
-        <v>140.5375203633166</v>
+        <v>139.8594654894129</v>
       </c>
       <c r="D64">
-        <v>251.9315203633166</v>
+        <v>253.2904654894129</v>
       </c>
       <c r="E64">
-        <v>111.794</v>
+        <v>113.831</v>
       </c>
       <c r="F64">
-        <v>126.294</v>
+        <v>128.331</v>
       </c>
       <c r="G64">
         <v>14.9</v>
@@ -6535,28 +6535,28 @@
         <v>32.9</v>
       </c>
       <c r="M64">
-        <v>6.9840582</v>
+        <v>7.0967043</v>
       </c>
       <c r="N64">
-        <v>25.9159418</v>
+        <v>25.8032957</v>
       </c>
       <c r="O64">
-        <v>9.070579629999999</v>
+        <v>9.031153495</v>
       </c>
       <c r="P64">
-        <v>16.84536217</v>
+        <v>16.772142205</v>
       </c>
       <c r="Q64">
-        <v>21.74536217</v>
+        <v>21.672142205</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4318794521122802</v>
+        <v>0.4405416192405457</v>
       </c>
       <c r="T64">
-        <v>1.896952041274824</v>
+        <v>1.939512492306152</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.71072821243099</v>
+        <v>4.635954748741609</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1856457491190019</v>
+        <v>0.1848914064353374</v>
       </c>
       <c r="C65">
-        <v>139.8594654894129</v>
+        <v>139.1961507111001</v>
       </c>
       <c r="D65">
-        <v>253.2904654894129</v>
+        <v>254.6641507111001</v>
       </c>
       <c r="E65">
-        <v>113.831</v>
+        <v>115.868</v>
       </c>
       <c r="F65">
-        <v>128.331</v>
+        <v>130.368</v>
       </c>
       <c r="G65">
         <v>14.9</v>
@@ -6617,28 +6617,28 @@
         <v>32.9</v>
       </c>
       <c r="M65">
-        <v>7.0967043</v>
+        <v>7.2093504</v>
       </c>
       <c r="N65">
-        <v>25.8032957</v>
+        <v>25.6906496</v>
       </c>
       <c r="O65">
-        <v>9.031153495</v>
+        <v>8.991727359999999</v>
       </c>
       <c r="P65">
-        <v>16.772142205</v>
+        <v>16.69892224</v>
       </c>
       <c r="Q65">
-        <v>21.672142205</v>
+        <v>21.59892224</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4405416192405457</v>
+        <v>0.4496850178759373</v>
       </c>
       <c r="T65">
-        <v>1.939512492306152</v>
+        <v>1.984437412839223</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.635954748741609</v>
+        <v>4.563517955792522</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1848914064353374</v>
+        <v>0.1851933137516729</v>
       </c>
       <c r="C66">
-        <v>139.1961507111001</v>
+        <v>136.6075821441529</v>
       </c>
       <c r="D66">
-        <v>254.6641507111001</v>
+        <v>254.1125821441529</v>
       </c>
       <c r="E66">
-        <v>115.868</v>
+        <v>117.905</v>
       </c>
       <c r="F66">
-        <v>130.368</v>
+        <v>132.405</v>
       </c>
       <c r="G66">
         <v>14.9</v>
@@ -6699,45 +6699,45 @@
         <v>32.9</v>
       </c>
       <c r="M66">
-        <v>7.2093504</v>
+        <v>7.653009000000001</v>
       </c>
       <c r="N66">
-        <v>25.6906496</v>
+        <v>25.246991</v>
       </c>
       <c r="O66">
-        <v>8.991727359999999</v>
+        <v>8.836446849999998</v>
       </c>
       <c r="P66">
-        <v>16.69892224</v>
+        <v>16.41054415</v>
       </c>
       <c r="Q66">
-        <v>21.59892224</v>
+        <v>21.31054415</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4496850178759373</v>
+        <v>0.4593508964333511</v>
       </c>
       <c r="T66">
-        <v>1.984437412839223</v>
+        <v>2.031929471688467</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.35</v>
       </c>
       <c r="W66">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.563517955792522</v>
+        <v>4.298962669454589</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1851933137516729</v>
+        <v>0.1844552210680083</v>
       </c>
       <c r="C67">
-        <v>136.6075821441529</v>
+        <v>135.9232801259744</v>
       </c>
       <c r="D67">
-        <v>254.1125821441529</v>
+        <v>255.4652801259744</v>
       </c>
       <c r="E67">
-        <v>117.905</v>
+        <v>119.942</v>
       </c>
       <c r="F67">
-        <v>132.405</v>
+        <v>134.442</v>
       </c>
       <c r="G67">
         <v>14.9</v>
@@ -6781,28 +6781,28 @@
         <v>32.9</v>
       </c>
       <c r="M67">
-        <v>7.653009000000001</v>
+        <v>7.770747600000001</v>
       </c>
       <c r="N67">
-        <v>25.246991</v>
+        <v>25.1292524</v>
       </c>
       <c r="O67">
-        <v>8.836446849999998</v>
+        <v>8.795238339999999</v>
       </c>
       <c r="P67">
-        <v>16.41054415</v>
+        <v>16.33401406</v>
       </c>
       <c r="Q67">
-        <v>21.31054415</v>
+        <v>21.23401406</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4593508964333511</v>
+        <v>0.4695853560823774</v>
       </c>
       <c r="T67">
-        <v>2.031929471688467</v>
+        <v>2.082215181058256</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.298962669454589</v>
+        <v>4.23382687143255</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1844552210680083</v>
+        <v>0.1837171283843438</v>
       </c>
       <c r="C68">
-        <v>135.9232801259744</v>
+        <v>135.2534566065187</v>
       </c>
       <c r="D68">
-        <v>255.4652801259744</v>
+        <v>256.8324566065187</v>
       </c>
       <c r="E68">
-        <v>119.942</v>
+        <v>121.979</v>
       </c>
       <c r="F68">
-        <v>134.442</v>
+        <v>136.479</v>
       </c>
       <c r="G68">
         <v>14.9</v>
@@ -6863,28 +6863,28 @@
         <v>32.9</v>
       </c>
       <c r="M68">
-        <v>7.770747600000001</v>
+        <v>7.888486200000002</v>
       </c>
       <c r="N68">
-        <v>25.1292524</v>
+        <v>25.0115138</v>
       </c>
       <c r="O68">
-        <v>8.795238339999999</v>
+        <v>8.754029829999999</v>
       </c>
       <c r="P68">
-        <v>16.33401406</v>
+        <v>16.25748397</v>
       </c>
       <c r="Q68">
-        <v>21.23401406</v>
+        <v>21.15748396999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4695853560823774</v>
+        <v>0.4804400860131632</v>
       </c>
       <c r="T68">
-        <v>2.082215181058256</v>
+        <v>2.13554850917773</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.23382687143255</v>
+        <v>4.170635425590272</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1837171283843438</v>
+        <v>0.1829790357006793</v>
       </c>
       <c r="C69">
-        <v>135.2534566065187</v>
+        <v>134.5983452907524</v>
       </c>
       <c r="D69">
-        <v>256.8324566065187</v>
+        <v>258.2143452907524</v>
       </c>
       <c r="E69">
-        <v>121.979</v>
+        <v>124.016</v>
       </c>
       <c r="F69">
-        <v>136.479</v>
+        <v>138.516</v>
       </c>
       <c r="G69">
         <v>14.9</v>
@@ -6945,28 +6945,28 @@
         <v>32.9</v>
       </c>
       <c r="M69">
-        <v>7.888486200000002</v>
+        <v>8.0062248</v>
       </c>
       <c r="N69">
-        <v>25.0115138</v>
+        <v>24.8937752</v>
       </c>
       <c r="O69">
-        <v>8.754029829999999</v>
+        <v>8.71282132</v>
       </c>
       <c r="P69">
-        <v>16.25748397</v>
+        <v>16.18095388</v>
       </c>
       <c r="Q69">
-        <v>21.15748396999999</v>
+        <v>21.08095388</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4804400860131632</v>
+        <v>0.4919732365646228</v>
       </c>
       <c r="T69">
-        <v>2.13554850917773</v>
+        <v>2.19221517030467</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.170635425590272</v>
+        <v>4.109302551684534</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1829790357006793</v>
+        <v>0.1822409430170147</v>
       </c>
       <c r="C70">
-        <v>134.5983452907524</v>
+        <v>133.9581849406555</v>
       </c>
       <c r="D70">
-        <v>258.2143452907524</v>
+        <v>259.6111849406555</v>
       </c>
       <c r="E70">
-        <v>124.016</v>
+        <v>126.053</v>
       </c>
       <c r="F70">
-        <v>138.516</v>
+        <v>140.553</v>
       </c>
       <c r="G70">
         <v>14.9</v>
@@ -7027,28 +7027,28 @@
         <v>32.9</v>
       </c>
       <c r="M70">
-        <v>8.0062248</v>
+        <v>8.123963400000001</v>
       </c>
       <c r="N70">
-        <v>24.8937752</v>
+        <v>24.7760366</v>
       </c>
       <c r="O70">
-        <v>8.71282132</v>
+        <v>8.671612809999999</v>
       </c>
       <c r="P70">
-        <v>16.18095388</v>
+        <v>16.10442379</v>
       </c>
       <c r="Q70">
-        <v>21.08095388</v>
+        <v>21.00442379</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4919732365646228</v>
+        <v>0.5042504613452088</v>
       </c>
       <c r="T70">
-        <v>2.19221517030467</v>
+        <v>2.252537745052702</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.109302551684534</v>
+        <v>4.049747442239831</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1822409430170147</v>
+        <v>0.1830953503333502</v>
       </c>
       <c r="C71">
-        <v>133.9581849406555</v>
+        <v>130.3055898365442</v>
       </c>
       <c r="D71">
-        <v>259.6111849406555</v>
+        <v>257.9955898365442</v>
       </c>
       <c r="E71">
-        <v>126.053</v>
+        <v>128.09</v>
       </c>
       <c r="F71">
-        <v>140.553</v>
+        <v>142.59</v>
       </c>
       <c r="G71">
         <v>14.9</v>
@@ -7109,45 +7109,45 @@
         <v>32.9</v>
       </c>
       <c r="M71">
-        <v>8.123963400000001</v>
+        <v>8.740767</v>
       </c>
       <c r="N71">
-        <v>24.7760366</v>
+        <v>24.159233</v>
       </c>
       <c r="O71">
-        <v>8.671612809999999</v>
+        <v>8.455731549999999</v>
       </c>
       <c r="P71">
-        <v>16.10442379</v>
+        <v>15.70350145</v>
       </c>
       <c r="Q71">
-        <v>21.00442379</v>
+        <v>20.60350145</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5042504613452088</v>
+        <v>0.5173461677778339</v>
       </c>
       <c r="T71">
-        <v>2.252537745052702</v>
+        <v>2.316881824783938</v>
       </c>
       <c r="U71">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.35</v>
       </c>
       <c r="W71">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.049747442239831</v>
+        <v>3.763971742983196</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1830953503333502</v>
+        <v>0.1823800076496856</v>
       </c>
       <c r="C72">
-        <v>130.3055898365442</v>
+        <v>129.6198509821772</v>
       </c>
       <c r="D72">
-        <v>257.9955898365442</v>
+        <v>259.3468509821772</v>
       </c>
       <c r="E72">
-        <v>128.09</v>
+        <v>130.127</v>
       </c>
       <c r="F72">
-        <v>142.59</v>
+        <v>144.627</v>
       </c>
       <c r="G72">
         <v>14.9</v>
@@ -7191,28 +7191,28 @@
         <v>32.9</v>
       </c>
       <c r="M72">
-        <v>8.740767</v>
+        <v>8.8656351</v>
       </c>
       <c r="N72">
-        <v>24.159233</v>
+        <v>24.0343649</v>
       </c>
       <c r="O72">
-        <v>8.455731549999999</v>
+        <v>8.412027714999999</v>
       </c>
       <c r="P72">
-        <v>15.70350145</v>
+        <v>15.622337185</v>
       </c>
       <c r="Q72">
-        <v>20.60350145</v>
+        <v>20.522337185</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5173461677778339</v>
+        <v>0.5313450263782264</v>
       </c>
       <c r="T72">
-        <v>2.316881824783938</v>
+        <v>2.385663427255258</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.763971742983196</v>
+        <v>3.710958056462306</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1823800076496857</v>
+        <v>0.1816646649660211</v>
       </c>
       <c r="C73">
-        <v>129.6198509821772</v>
+        <v>128.9483412104713</v>
       </c>
       <c r="D73">
-        <v>259.3468509821772</v>
+        <v>260.7123412104713</v>
       </c>
       <c r="E73">
-        <v>130.127</v>
+        <v>132.164</v>
       </c>
       <c r="F73">
-        <v>144.627</v>
+        <v>146.664</v>
       </c>
       <c r="G73">
         <v>14.9</v>
@@ -7273,28 +7273,28 @@
         <v>32.9</v>
       </c>
       <c r="M73">
-        <v>8.865635099999999</v>
+        <v>8.990503199999999</v>
       </c>
       <c r="N73">
-        <v>24.0343649</v>
+        <v>23.9094968</v>
       </c>
       <c r="O73">
-        <v>8.412027714999999</v>
+        <v>8.36832388</v>
       </c>
       <c r="P73">
-        <v>15.622337185</v>
+        <v>15.54117292</v>
       </c>
       <c r="Q73">
-        <v>20.522337185</v>
+        <v>20.44117292</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5313450263782263</v>
+        <v>0.5463438034500753</v>
       </c>
       <c r="T73">
-        <v>2.385663427255257</v>
+        <v>2.459358001331672</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.710958056462306</v>
+        <v>3.659416972344774</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1816646649660211</v>
+        <v>0.1809493222823565</v>
       </c>
       <c r="C74">
-        <v>128.9483412104713</v>
+        <v>128.2912864641835</v>
       </c>
       <c r="D74">
-        <v>260.7123412104713</v>
+        <v>262.0922864641835</v>
       </c>
       <c r="E74">
-        <v>132.164</v>
+        <v>134.201</v>
       </c>
       <c r="F74">
-        <v>146.664</v>
+        <v>148.701</v>
       </c>
       <c r="G74">
         <v>14.9</v>
@@ -7355,28 +7355,28 @@
         <v>32.9</v>
       </c>
       <c r="M74">
-        <v>8.990503199999999</v>
+        <v>9.1153713</v>
       </c>
       <c r="N74">
-        <v>23.9094968</v>
+        <v>23.7846287</v>
       </c>
       <c r="O74">
-        <v>8.36832388</v>
+        <v>8.324620045</v>
       </c>
       <c r="P74">
-        <v>15.54117292</v>
+        <v>15.460008655</v>
       </c>
       <c r="Q74">
-        <v>20.44117292</v>
+        <v>20.360008655</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5463438034500753</v>
+        <v>0.5624536010457649</v>
       </c>
       <c r="T74">
-        <v>2.459358001331672</v>
+        <v>2.53851143274708</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.659416972344774</v>
+        <v>3.609287972723612</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1809493222823565</v>
+        <v>0.180233979598692</v>
       </c>
       <c r="C75">
-        <v>128.2912864641835</v>
+        <v>127.648917495168</v>
       </c>
       <c r="D75">
-        <v>262.0922864641835</v>
+        <v>263.486917495168</v>
       </c>
       <c r="E75">
-        <v>134.201</v>
+        <v>136.238</v>
       </c>
       <c r="F75">
-        <v>148.701</v>
+        <v>150.738</v>
       </c>
       <c r="G75">
         <v>14.9</v>
@@ -7437,28 +7437,28 @@
         <v>32.9</v>
       </c>
       <c r="M75">
-        <v>9.1153713</v>
+        <v>9.2402394</v>
       </c>
       <c r="N75">
-        <v>23.7846287</v>
+        <v>23.6597606</v>
       </c>
       <c r="O75">
-        <v>8.324620045</v>
+        <v>8.280916209999999</v>
       </c>
       <c r="P75">
-        <v>15.460008655</v>
+        <v>15.37884439</v>
       </c>
       <c r="Q75">
-        <v>20.360008655</v>
+        <v>20.27884439</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5624536010457649</v>
+        <v>0.5798026138411231</v>
       </c>
       <c r="T75">
-        <v>2.53851143274708</v>
+        <v>2.623753589655982</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.609287972723612</v>
+        <v>3.56051381093005</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.180233979598692</v>
+        <v>0.1795186369150275</v>
       </c>
       <c r="C76">
-        <v>127.648917495168</v>
+        <v>127.021469993009</v>
       </c>
       <c r="D76">
-        <v>263.486917495168</v>
+        <v>264.896469993009</v>
       </c>
       <c r="E76">
-        <v>136.238</v>
+        <v>138.275</v>
       </c>
       <c r="F76">
-        <v>150.738</v>
+        <v>152.775</v>
       </c>
       <c r="G76">
         <v>14.9</v>
@@ -7519,28 +7519,28 @@
         <v>32.9</v>
       </c>
       <c r="M76">
-        <v>9.2402394</v>
+        <v>9.365107499999999</v>
       </c>
       <c r="N76">
-        <v>23.6597606</v>
+        <v>23.5348925</v>
       </c>
       <c r="O76">
-        <v>8.280916209999999</v>
+        <v>8.237212374999999</v>
       </c>
       <c r="P76">
-        <v>15.37884439</v>
+        <v>15.297680125</v>
       </c>
       <c r="Q76">
-        <v>20.27884439</v>
+        <v>20.197680125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5798026138411231</v>
+        <v>0.59853954766011</v>
       </c>
       <c r="T76">
-        <v>2.623753589655982</v>
+        <v>2.715815119117595</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.56051381093005</v>
+        <v>3.513040293450983</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1795186369150275</v>
+        <v>0.180186494231363</v>
       </c>
       <c r="C77">
-        <v>127.021469993009</v>
+        <v>123.6680204005992</v>
       </c>
       <c r="D77">
-        <v>264.896469993009</v>
+        <v>263.5800204005992</v>
       </c>
       <c r="E77">
-        <v>138.275</v>
+        <v>140.312</v>
       </c>
       <c r="F77">
-        <v>152.775</v>
+        <v>154.812</v>
       </c>
       <c r="G77">
         <v>14.9</v>
@@ -7601,45 +7601,45 @@
         <v>32.9</v>
       </c>
       <c r="M77">
-        <v>9.365107499999999</v>
+        <v>9.9234492</v>
       </c>
       <c r="N77">
-        <v>23.5348925</v>
+        <v>22.9765508</v>
       </c>
       <c r="O77">
-        <v>8.237212374999999</v>
+        <v>8.04179278</v>
       </c>
       <c r="P77">
-        <v>15.297680125</v>
+        <v>14.93475802</v>
       </c>
       <c r="Q77">
-        <v>20.197680125</v>
+        <v>19.83475802</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.59853954766011</v>
+        <v>0.618837892630679</v>
       </c>
       <c r="T77">
-        <v>2.715815119117595</v>
+        <v>2.81554844270101</v>
       </c>
       <c r="U77">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.513040293450983</v>
+        <v>3.315379495266626</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.180186494231363</v>
+        <v>0.1794893515476984</v>
       </c>
       <c r="C78">
-        <v>123.6680204005992</v>
+        <v>123.0054969812329</v>
       </c>
       <c r="D78">
-        <v>263.5800204005992</v>
+        <v>264.9544969812329</v>
       </c>
       <c r="E78">
-        <v>140.312</v>
+        <v>142.349</v>
       </c>
       <c r="F78">
-        <v>154.812</v>
+        <v>156.849</v>
       </c>
       <c r="G78">
         <v>14.9</v>
@@ -7683,28 +7683,28 @@
         <v>32.9</v>
       </c>
       <c r="M78">
-        <v>9.9234492</v>
+        <v>10.0540209</v>
       </c>
       <c r="N78">
-        <v>22.9765508</v>
+        <v>22.8459791</v>
       </c>
       <c r="O78">
-        <v>8.04179278</v>
+        <v>7.996092685</v>
       </c>
       <c r="P78">
-        <v>14.93475802</v>
+        <v>14.849886415</v>
       </c>
       <c r="Q78">
-        <v>19.83475802</v>
+        <v>19.749886415</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.618837892630679</v>
+        <v>0.6409013110769497</v>
       </c>
       <c r="T78">
-        <v>2.81554844270101</v>
+        <v>2.923954229204722</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.315379495266626</v>
+        <v>3.272322618704722</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1794893515476984</v>
+        <v>0.1787922088640339</v>
       </c>
       <c r="C79">
-        <v>123.0054969812329</v>
+        <v>122.3573835231757</v>
       </c>
       <c r="D79">
-        <v>264.9544969812329</v>
+        <v>266.3433835231757</v>
       </c>
       <c r="E79">
-        <v>142.349</v>
+        <v>144.386</v>
       </c>
       <c r="F79">
-        <v>156.849</v>
+        <v>158.886</v>
       </c>
       <c r="G79">
         <v>14.9</v>
@@ -7765,28 +7765,28 @@
         <v>32.9</v>
       </c>
       <c r="M79">
-        <v>10.0540209</v>
+        <v>10.1845926</v>
       </c>
       <c r="N79">
-        <v>22.8459791</v>
+        <v>22.7154074</v>
       </c>
       <c r="O79">
-        <v>7.996092685</v>
+        <v>7.950392589999998</v>
       </c>
       <c r="P79">
-        <v>14.849886415</v>
+        <v>14.76501481</v>
       </c>
       <c r="Q79">
-        <v>19.749886415</v>
+        <v>19.66501481</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6409013110769497</v>
+        <v>0.6649704948365176</v>
       </c>
       <c r="T79">
-        <v>2.923954229204722</v>
+        <v>3.04221508720877</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.272322618704722</v>
+        <v>3.230369764618763</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1787922088640339</v>
+        <v>0.1780950661803693</v>
       </c>
       <c r="C80">
-        <v>122.3573835231757</v>
+        <v>121.7239078308205</v>
       </c>
       <c r="D80">
-        <v>266.3433835231757</v>
+        <v>267.7469078308205</v>
       </c>
       <c r="E80">
-        <v>144.386</v>
+        <v>146.423</v>
       </c>
       <c r="F80">
-        <v>158.886</v>
+        <v>160.923</v>
       </c>
       <c r="G80">
         <v>14.9</v>
@@ -7847,28 +7847,28 @@
         <v>32.9</v>
       </c>
       <c r="M80">
-        <v>10.1845926</v>
+        <v>10.3151643</v>
       </c>
       <c r="N80">
-        <v>22.7154074</v>
+        <v>22.5848357</v>
       </c>
       <c r="O80">
-        <v>7.950392589999998</v>
+        <v>7.904692494999999</v>
       </c>
       <c r="P80">
-        <v>14.76501481</v>
+        <v>14.680143205</v>
       </c>
       <c r="Q80">
-        <v>19.66501481</v>
+        <v>19.580143205</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6649704948365176</v>
+        <v>0.6913319818112826</v>
       </c>
       <c r="T80">
-        <v>3.04221508720877</v>
+        <v>3.171738884070348</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.230369764618763</v>
+        <v>3.189479008104601</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1780950661803693</v>
+        <v>0.1773979234967048</v>
       </c>
       <c r="C81">
-        <v>121.7239078308205</v>
+        <v>121.1053025357548</v>
       </c>
       <c r="D81">
-        <v>267.7469078308205</v>
+        <v>269.1653025357548</v>
       </c>
       <c r="E81">
-        <v>146.423</v>
+        <v>148.46</v>
       </c>
       <c r="F81">
-        <v>160.923</v>
+        <v>162.96</v>
       </c>
       <c r="G81">
         <v>14.9</v>
@@ -7929,28 +7929,28 @@
         <v>32.9</v>
       </c>
       <c r="M81">
-        <v>10.3151643</v>
+        <v>10.445736</v>
       </c>
       <c r="N81">
-        <v>22.5848357</v>
+        <v>22.45426399999999</v>
       </c>
       <c r="O81">
-        <v>7.904692494999999</v>
+        <v>7.858992399999997</v>
       </c>
       <c r="P81">
-        <v>14.680143205</v>
+        <v>14.5952716</v>
       </c>
       <c r="Q81">
-        <v>19.580143205</v>
+        <v>19.4952716</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6913319818112826</v>
+        <v>0.7203296174835241</v>
       </c>
       <c r="T81">
-        <v>3.171738884070348</v>
+        <v>3.314215060618083</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.189479008104601</v>
+        <v>3.149610520503293</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1773979234967048</v>
+        <v>0.1767007808130402</v>
       </c>
       <c r="C82">
-        <v>121.1053025357548</v>
+        <v>120.5018052253006</v>
       </c>
       <c r="D82">
-        <v>269.1653025357548</v>
+        <v>270.5988052253007</v>
       </c>
       <c r="E82">
-        <v>148.46</v>
+        <v>150.497</v>
       </c>
       <c r="F82">
-        <v>162.96</v>
+        <v>164.997</v>
       </c>
       <c r="G82">
         <v>14.9</v>
@@ -8011,28 +8011,28 @@
         <v>32.9</v>
       </c>
       <c r="M82">
-        <v>10.445736</v>
+        <v>10.5763077</v>
       </c>
       <c r="N82">
-        <v>22.45426399999999</v>
+        <v>22.3236923</v>
       </c>
       <c r="O82">
-        <v>7.858992399999997</v>
+        <v>7.813292304999998</v>
       </c>
       <c r="P82">
-        <v>14.5952716</v>
+        <v>14.510399995</v>
       </c>
       <c r="Q82">
-        <v>19.4952716</v>
+        <v>19.410399995</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.7203296174835241</v>
+        <v>0.7523796358581069</v>
       </c>
       <c r="T82">
-        <v>3.314215060618083</v>
+        <v>3.471688729434001</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.149610520503293</v>
+        <v>3.110726440003253</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1767007808130402</v>
+        <v>0.1760036381293757</v>
       </c>
       <c r="C83">
-        <v>120.5018052253006</v>
+        <v>119.9136585751873</v>
       </c>
       <c r="D83">
-        <v>270.5988052253007</v>
+        <v>272.0476585751873</v>
       </c>
       <c r="E83">
-        <v>150.497</v>
+        <v>152.534</v>
       </c>
       <c r="F83">
-        <v>164.997</v>
+        <v>167.034</v>
       </c>
       <c r="G83">
         <v>14.9</v>
@@ -8093,28 +8093,28 @@
         <v>32.9</v>
       </c>
       <c r="M83">
-        <v>10.5763077</v>
+        <v>10.7068794</v>
       </c>
       <c r="N83">
-        <v>22.3236923</v>
+        <v>22.1931206</v>
       </c>
       <c r="O83">
-        <v>7.813292304999998</v>
+        <v>7.767592209999999</v>
       </c>
       <c r="P83">
-        <v>14.510399995</v>
+        <v>14.42552839</v>
       </c>
       <c r="Q83">
-        <v>19.410399995</v>
+        <v>19.32552839</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7523796358581069</v>
+        <v>0.7879907673854208</v>
       </c>
       <c r="T83">
-        <v>3.471688729434001</v>
+        <v>3.646659472562798</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.110726440003253</v>
+        <v>3.072790751710531</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1760036381293757</v>
+        <v>0.1753064954457112</v>
       </c>
       <c r="C84">
-        <v>119.9136585751873</v>
+        <v>119.3411104865068</v>
       </c>
       <c r="D84">
-        <v>272.0476585751873</v>
+        <v>273.5121104865068</v>
       </c>
       <c r="E84">
-        <v>152.534</v>
+        <v>154.571</v>
       </c>
       <c r="F84">
-        <v>167.034</v>
+        <v>169.071</v>
       </c>
       <c r="G84">
         <v>14.9</v>
@@ -8175,28 +8175,28 @@
         <v>32.9</v>
       </c>
       <c r="M84">
-        <v>10.7068794</v>
+        <v>10.8374511</v>
       </c>
       <c r="N84">
-        <v>22.1931206</v>
+        <v>22.0625489</v>
       </c>
       <c r="O84">
-        <v>7.767592209999999</v>
+        <v>7.721892114999998</v>
       </c>
       <c r="P84">
-        <v>14.42552839</v>
+        <v>14.340656785</v>
       </c>
       <c r="Q84">
-        <v>19.32552839</v>
+        <v>19.240656785</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7879907673854208</v>
+        <v>0.8277914437983015</v>
       </c>
       <c r="T84">
-        <v>3.646659472562798</v>
+        <v>3.842215009000867</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.072790751710531</v>
+        <v>3.035769176388717</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1753064954457112</v>
+        <v>0.1788681527620467</v>
       </c>
       <c r="C85">
-        <v>119.3411104865068</v>
+        <v>109.9833775447742</v>
       </c>
       <c r="D85">
-        <v>273.5121104865068</v>
+        <v>266.1913775447742</v>
       </c>
       <c r="E85">
-        <v>154.571</v>
+        <v>156.608</v>
       </c>
       <c r="F85">
-        <v>169.071</v>
+        <v>171.108</v>
       </c>
       <c r="G85">
         <v>14.9</v>
@@ -8257,45 +8257,45 @@
         <v>32.9</v>
       </c>
       <c r="M85">
-        <v>10.8374511</v>
+        <v>12.3026652</v>
       </c>
       <c r="N85">
-        <v>22.0625489</v>
+        <v>20.5973348</v>
       </c>
       <c r="O85">
-        <v>7.721892114999998</v>
+        <v>7.209067179999999</v>
       </c>
       <c r="P85">
-        <v>14.340656785</v>
+        <v>13.38826762</v>
       </c>
       <c r="Q85">
-        <v>19.240656785</v>
+        <v>18.28826762</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.8277914437983015</v>
+        <v>0.8725672047627919</v>
       </c>
       <c r="T85">
-        <v>3.842215009000867</v>
+        <v>4.062214987493693</v>
       </c>
       <c r="U85">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V85">
         <v>0.35</v>
       </c>
       <c r="W85">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.035769176388717</v>
+        <v>2.674217290737945</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1788681527620467</v>
+        <v>0.1782217100783821</v>
       </c>
       <c r="C86">
-        <v>109.9833775447742</v>
+        <v>109.2458432318322</v>
       </c>
       <c r="D86">
-        <v>266.1913775447742</v>
+        <v>267.4908432318322</v>
       </c>
       <c r="E86">
-        <v>156.608</v>
+        <v>158.645</v>
       </c>
       <c r="F86">
-        <v>171.108</v>
+        <v>173.145</v>
       </c>
       <c r="G86">
         <v>14.9</v>
@@ -8339,28 +8339,28 @@
         <v>32.9</v>
       </c>
       <c r="M86">
-        <v>12.3026652</v>
+        <v>12.4491255</v>
       </c>
       <c r="N86">
-        <v>20.5973348</v>
+        <v>20.4508745</v>
       </c>
       <c r="O86">
-        <v>7.209067179999999</v>
+        <v>7.157806074999999</v>
       </c>
       <c r="P86">
-        <v>13.38826762</v>
+        <v>13.293068425</v>
       </c>
       <c r="Q86">
-        <v>18.28826762</v>
+        <v>18.193068425</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8725672047627916</v>
+        <v>0.923313067189214</v>
       </c>
       <c r="T86">
-        <v>4.062214987493691</v>
+        <v>4.311548296452227</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.674217290737945</v>
+        <v>2.64275591084691</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1782217100783821</v>
+        <v>0.1775752673947176</v>
       </c>
       <c r="C87">
-        <v>109.2458432318322</v>
+        <v>108.5210583536313</v>
       </c>
       <c r="D87">
-        <v>267.4908432318322</v>
+        <v>268.8030583536313</v>
       </c>
       <c r="E87">
-        <v>158.645</v>
+        <v>160.682</v>
       </c>
       <c r="F87">
-        <v>173.145</v>
+        <v>175.182</v>
       </c>
       <c r="G87">
         <v>14.9</v>
@@ -8421,28 +8421,28 @@
         <v>32.9</v>
       </c>
       <c r="M87">
-        <v>12.4491255</v>
+        <v>12.5955858</v>
       </c>
       <c r="N87">
-        <v>20.4508745</v>
+        <v>20.3044142</v>
       </c>
       <c r="O87">
-        <v>7.157806074999999</v>
+        <v>7.106544969999998</v>
       </c>
       <c r="P87">
-        <v>13.293068425</v>
+        <v>13.19786923</v>
       </c>
       <c r="Q87">
-        <v>18.193068425</v>
+        <v>18.09786923</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.923313067189214</v>
+        <v>0.981308338533697</v>
       </c>
       <c r="T87">
-        <v>4.311548296452227</v>
+        <v>4.596500649547698</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.64275591084691</v>
+        <v>2.612026190953341</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1775752673947176</v>
+        <v>0.1769288247110531</v>
       </c>
       <c r="C88">
-        <v>108.5210583536313</v>
+        <v>107.8092114677712</v>
       </c>
       <c r="D88">
-        <v>268.8030583536313</v>
+        <v>270.1282114677712</v>
       </c>
       <c r="E88">
-        <v>160.682</v>
+        <v>162.719</v>
       </c>
       <c r="F88">
-        <v>175.182</v>
+        <v>177.219</v>
       </c>
       <c r="G88">
         <v>14.9</v>
@@ -8503,28 +8503,28 @@
         <v>32.9</v>
       </c>
       <c r="M88">
-        <v>12.5955858</v>
+        <v>12.7420461</v>
       </c>
       <c r="N88">
-        <v>20.3044142</v>
+        <v>20.1579539</v>
       </c>
       <c r="O88">
-        <v>7.106544969999998</v>
+        <v>7.055283864999998</v>
       </c>
       <c r="P88">
-        <v>13.19786923</v>
+        <v>13.102670035</v>
       </c>
       <c r="Q88">
-        <v>18.09786923</v>
+        <v>18.00267003499999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.981308338533697</v>
+        <v>1.048225959315793</v>
       </c>
       <c r="T88">
-        <v>4.596500649547698</v>
+        <v>4.925291826196316</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.612026190953341</v>
+        <v>2.582002901402153</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1769288247110531</v>
+        <v>0.1762823820273886</v>
       </c>
       <c r="C89">
-        <v>107.8092114677712</v>
+        <v>107.1104948684994</v>
       </c>
       <c r="D89">
-        <v>270.1282114677712</v>
+        <v>271.4664948684994</v>
       </c>
       <c r="E89">
-        <v>162.719</v>
+        <v>164.756</v>
       </c>
       <c r="F89">
-        <v>177.219</v>
+        <v>179.256</v>
       </c>
       <c r="G89">
         <v>14.9</v>
@@ -8585,28 +8585,28 @@
         <v>32.9</v>
       </c>
       <c r="M89">
-        <v>12.7420461</v>
+        <v>12.8885064</v>
       </c>
       <c r="N89">
-        <v>20.1579539</v>
+        <v>20.0114936</v>
       </c>
       <c r="O89">
-        <v>7.055283864999998</v>
+        <v>7.004022759999999</v>
       </c>
       <c r="P89">
-        <v>13.102670035</v>
+        <v>13.00747084</v>
       </c>
       <c r="Q89">
-        <v>18.00267003499999</v>
+        <v>17.90747084</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.048225959315793</v>
+        <v>1.126296516894904</v>
       </c>
       <c r="T89">
-        <v>4.925291826196316</v>
+        <v>5.308881532286374</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.582002901402153</v>
+        <v>2.552661959340766</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1762823820273886</v>
+        <v>0.175635939343724</v>
       </c>
       <c r="C90">
-        <v>107.1104948684994</v>
+        <v>106.4251046797337</v>
       </c>
       <c r="D90">
-        <v>271.4664948684994</v>
+        <v>272.8181046797337</v>
       </c>
       <c r="E90">
-        <v>164.756</v>
+        <v>166.793</v>
       </c>
       <c r="F90">
-        <v>179.256</v>
+        <v>181.293</v>
       </c>
       <c r="G90">
         <v>14.9</v>
@@ -8667,28 +8667,28 @@
         <v>32.9</v>
       </c>
       <c r="M90">
-        <v>12.8885064</v>
+        <v>13.0349667</v>
       </c>
       <c r="N90">
-        <v>20.0114936</v>
+        <v>19.8650333</v>
       </c>
       <c r="O90">
-        <v>7.004022759999999</v>
+        <v>6.952761654999999</v>
       </c>
       <c r="P90">
-        <v>13.00747084</v>
+        <v>12.912271645</v>
       </c>
       <c r="Q90">
-        <v>17.90747084</v>
+        <v>17.812271645</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.126296516894904</v>
+        <v>1.218561721306582</v>
       </c>
       <c r="T90">
-        <v>5.308881532286374</v>
+        <v>5.762214821301894</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.552661959340766</v>
+        <v>2.523980364291993</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.175635939343724</v>
+        <v>0.1772709966600594</v>
       </c>
       <c r="C91">
-        <v>106.4251046797337</v>
+        <v>100.9951644159677</v>
       </c>
       <c r="D91">
-        <v>272.8181046797337</v>
+        <v>269.4251644159677</v>
       </c>
       <c r="E91">
-        <v>166.793</v>
+        <v>168.83</v>
       </c>
       <c r="F91">
-        <v>181.293</v>
+        <v>183.33</v>
       </c>
       <c r="G91">
         <v>14.9</v>
@@ -8749,45 +8749,45 @@
         <v>32.9</v>
       </c>
       <c r="M91">
-        <v>13.0349667</v>
+        <v>13.896414</v>
       </c>
       <c r="N91">
-        <v>19.8650333</v>
+        <v>19.003586</v>
       </c>
       <c r="O91">
-        <v>6.952761654999999</v>
+        <v>6.651255099999999</v>
       </c>
       <c r="P91">
-        <v>12.912271645</v>
+        <v>12.3523309</v>
       </c>
       <c r="Q91">
-        <v>17.812271645</v>
+        <v>17.2523309</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.218561721306582</v>
+        <v>1.329279966600595</v>
       </c>
       <c r="T91">
-        <v>5.762214821301894</v>
+        <v>6.306214768120519</v>
       </c>
       <c r="U91">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V91">
         <v>0.35</v>
       </c>
       <c r="W91">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.523980364291993</v>
+        <v>2.367517260208281</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1772709966600594</v>
+        <v>0.1766499039763949</v>
       </c>
       <c r="C92">
-        <v>100.9951644159677</v>
+        <v>100.2370189915435</v>
       </c>
       <c r="D92">
-        <v>269.4251644159677</v>
+        <v>270.7040189915435</v>
       </c>
       <c r="E92">
-        <v>168.83</v>
+        <v>170.867</v>
       </c>
       <c r="F92">
-        <v>183.33</v>
+        <v>185.367</v>
       </c>
       <c r="G92">
         <v>14.9</v>
@@ -8831,28 +8831,28 @@
         <v>32.9</v>
       </c>
       <c r="M92">
-        <v>13.896414</v>
+        <v>14.0508186</v>
       </c>
       <c r="N92">
-        <v>19.003586</v>
+        <v>18.8491814</v>
       </c>
       <c r="O92">
-        <v>6.651255099999999</v>
+        <v>6.59721349</v>
       </c>
       <c r="P92">
-        <v>12.3523309</v>
+        <v>12.25196791</v>
       </c>
       <c r="Q92">
-        <v>17.2523309</v>
+        <v>17.15196791</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.329279966600595</v>
+        <v>1.464602266404388</v>
       </c>
       <c r="T92">
-        <v>6.306214768120519</v>
+        <v>6.971103592009951</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.367517260208281</v>
+        <v>2.341500587019179</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1766499039763949</v>
+        <v>0.1760288112927304</v>
       </c>
       <c r="C93">
-        <v>100.2370189915435</v>
+        <v>99.49107190038325</v>
       </c>
       <c r="D93">
-        <v>270.7040189915435</v>
+        <v>271.9950719003833</v>
       </c>
       <c r="E93">
-        <v>170.867</v>
+        <v>172.904</v>
       </c>
       <c r="F93">
-        <v>185.367</v>
+        <v>187.404</v>
       </c>
       <c r="G93">
         <v>14.9</v>
@@ -8913,28 +8913,28 @@
         <v>32.9</v>
       </c>
       <c r="M93">
-        <v>14.0508186</v>
+        <v>14.2052232</v>
       </c>
       <c r="N93">
-        <v>18.8491814</v>
+        <v>18.6947768</v>
       </c>
       <c r="O93">
-        <v>6.59721349</v>
+        <v>6.543171879999999</v>
       </c>
       <c r="P93">
-        <v>12.25196791</v>
+        <v>12.15160492</v>
       </c>
       <c r="Q93">
-        <v>17.15196791</v>
+        <v>17.05160492</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.464602266404388</v>
+        <v>1.63375514115913</v>
       </c>
       <c r="T93">
-        <v>6.971103592009951</v>
+        <v>7.80221462187174</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.341500587019179</v>
+        <v>2.316049493682014</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1760288112927304</v>
+        <v>0.1754077186090658</v>
       </c>
       <c r="C94">
-        <v>99.49107190038325</v>
+        <v>98.75749850925448</v>
       </c>
       <c r="D94">
-        <v>271.9950719003833</v>
+        <v>273.2984985092545</v>
       </c>
       <c r="E94">
-        <v>172.904</v>
+        <v>174.941</v>
       </c>
       <c r="F94">
-        <v>187.404</v>
+        <v>189.441</v>
       </c>
       <c r="G94">
         <v>14.9</v>
@@ -8995,28 +8995,28 @@
         <v>32.9</v>
       </c>
       <c r="M94">
-        <v>14.2052232</v>
+        <v>14.3596278</v>
       </c>
       <c r="N94">
-        <v>18.6947768</v>
+        <v>18.5403722</v>
       </c>
       <c r="O94">
-        <v>6.543171879999999</v>
+        <v>6.489130269999999</v>
       </c>
       <c r="P94">
-        <v>12.15160492</v>
+        <v>12.05124193</v>
       </c>
       <c r="Q94">
-        <v>17.05160492</v>
+        <v>16.95124192999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.63375514115913</v>
+        <v>1.851237408700941</v>
       </c>
       <c r="T94">
-        <v>7.80221462187174</v>
+        <v>8.870785945979753</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.316049493682014</v>
+        <v>2.291145735685433</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1754077186090658</v>
+        <v>0.1747866259254013</v>
       </c>
       <c r="C95">
-        <v>98.75749850925448</v>
+        <v>98.03647756260818</v>
       </c>
       <c r="D95">
-        <v>273.2984985092545</v>
+        <v>274.6144775626082</v>
       </c>
       <c r="E95">
-        <v>174.941</v>
+        <v>176.978</v>
       </c>
       <c r="F95">
-        <v>189.441</v>
+        <v>191.478</v>
       </c>
       <c r="G95">
         <v>14.9</v>
@@ -9077,28 +9077,28 @@
         <v>32.9</v>
       </c>
       <c r="M95">
-        <v>14.3596278</v>
+        <v>14.5140324</v>
       </c>
       <c r="N95">
-        <v>18.5403722</v>
+        <v>18.3859676</v>
       </c>
       <c r="O95">
-        <v>6.489130269999999</v>
+        <v>6.435088659999999</v>
       </c>
       <c r="P95">
-        <v>12.05124193</v>
+        <v>11.95087894</v>
       </c>
       <c r="Q95">
-        <v>16.95124192999999</v>
+        <v>16.85087894</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.851237408700941</v>
+        <v>2.141213765423357</v>
       </c>
       <c r="T95">
-        <v>8.870785945979753</v>
+        <v>10.29554771145711</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.291145735685433</v>
+        <v>2.266771844880269</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1747866259254013</v>
+        <v>0.1741655332417368</v>
       </c>
       <c r="C96">
-        <v>98.03647756260818</v>
+        <v>97.32819126429391</v>
       </c>
       <c r="D96">
-        <v>274.6144775626082</v>
+        <v>275.9431912642939</v>
       </c>
       <c r="E96">
-        <v>176.978</v>
+        <v>179.015</v>
       </c>
       <c r="F96">
-        <v>191.478</v>
+        <v>193.515</v>
       </c>
       <c r="G96">
         <v>14.9</v>
@@ -9159,28 +9159,28 @@
         <v>32.9</v>
       </c>
       <c r="M96">
-        <v>14.5140324</v>
+        <v>14.668437</v>
       </c>
       <c r="N96">
-        <v>18.3859676</v>
+        <v>18.23156299999999</v>
       </c>
       <c r="O96">
-        <v>6.435088659999999</v>
+        <v>6.381047049999998</v>
       </c>
       <c r="P96">
-        <v>11.95087894</v>
+        <v>11.85051595</v>
       </c>
       <c r="Q96">
-        <v>16.85087894</v>
+        <v>16.75051594999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.141213765423357</v>
+        <v>2.547180664834738</v>
       </c>
       <c r="T96">
-        <v>10.29554771145711</v>
+        <v>12.29021418312541</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.266771844880269</v>
+        <v>2.242911088618371</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1741655332417368</v>
+        <v>0.1735444405580722</v>
       </c>
       <c r="C97">
-        <v>97.32819126429391</v>
+        <v>96.63282536165715</v>
       </c>
       <c r="D97">
-        <v>275.9431912642939</v>
+        <v>277.2848253616572</v>
       </c>
       <c r="E97">
-        <v>179.015</v>
+        <v>181.052</v>
       </c>
       <c r="F97">
-        <v>193.515</v>
+        <v>195.552</v>
       </c>
       <c r="G97">
         <v>14.9</v>
@@ -9241,28 +9241,28 @@
         <v>32.9</v>
       </c>
       <c r="M97">
-        <v>14.668437</v>
+        <v>14.8228416</v>
       </c>
       <c r="N97">
-        <v>18.23156299999999</v>
+        <v>18.0771584</v>
       </c>
       <c r="O97">
-        <v>6.381047049999998</v>
+        <v>6.327005439999999</v>
       </c>
       <c r="P97">
-        <v>11.85051595</v>
+        <v>11.75015296</v>
       </c>
       <c r="Q97">
-        <v>16.75051594999999</v>
+        <v>16.65015296</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.547180664834738</v>
+        <v>3.156131013951811</v>
       </c>
       <c r="T97">
-        <v>12.29021418312541</v>
+        <v>15.28221389062785</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.242911088618371</v>
+        <v>2.219547431445263</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1735444405580722</v>
+        <v>0.1729233478744077</v>
       </c>
       <c r="C98">
-        <v>96.63282536165715</v>
+        <v>95.95056923210225</v>
       </c>
       <c r="D98">
-        <v>277.2848253616572</v>
+        <v>278.6395692321022</v>
       </c>
       <c r="E98">
-        <v>181.052</v>
+        <v>183.089</v>
       </c>
       <c r="F98">
-        <v>195.552</v>
+        <v>197.589</v>
       </c>
       <c r="G98">
         <v>14.9</v>
@@ -9323,28 +9323,28 @@
         <v>32.9</v>
       </c>
       <c r="M98">
-        <v>14.8228416</v>
+        <v>14.9772462</v>
       </c>
       <c r="N98">
-        <v>18.0771584</v>
+        <v>17.9227538</v>
       </c>
       <c r="O98">
-        <v>6.327005439999999</v>
+        <v>6.272963829999999</v>
       </c>
       <c r="P98">
-        <v>11.75015296</v>
+        <v>11.64978997</v>
       </c>
       <c r="Q98">
-        <v>16.65015296</v>
+        <v>16.54978997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.156131013951803</v>
+        <v>4.171048262480253</v>
       </c>
       <c r="T98">
-        <v>15.28221389062781</v>
+        <v>20.26888006979854</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.219547431445263</v>
+        <v>2.196665499162322</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1729233478744077</v>
+        <v>0.1723022551907432</v>
       </c>
       <c r="C99">
-        <v>95.95056923210225</v>
+        <v>95.28161597220628</v>
       </c>
       <c r="D99">
-        <v>278.6395692321022</v>
+        <v>280.0076159722063</v>
       </c>
       <c r="E99">
-        <v>183.089</v>
+        <v>185.126</v>
       </c>
       <c r="F99">
-        <v>197.589</v>
+        <v>199.626</v>
       </c>
       <c r="G99">
         <v>14.9</v>
@@ -9405,28 +9405,28 @@
         <v>32.9</v>
       </c>
       <c r="M99">
-        <v>14.9772462</v>
+        <v>15.1316508</v>
       </c>
       <c r="N99">
-        <v>17.9227538</v>
+        <v>17.7683492</v>
       </c>
       <c r="O99">
-        <v>6.272963829999999</v>
+        <v>6.21892222</v>
       </c>
       <c r="P99">
-        <v>11.64978997</v>
+        <v>11.54942698</v>
       </c>
       <c r="Q99">
-        <v>16.54978997</v>
+        <v>16.44942698</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.171048262480253</v>
+        <v>6.200882759537152</v>
       </c>
       <c r="T99">
-        <v>20.26888006979854</v>
+        <v>30.24221242813998</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.196665499162322</v>
+        <v>2.174250545089238</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1723022551907432</v>
+        <v>0.1716811625070786</v>
       </c>
       <c r="C100">
-        <v>95.28161597220628</v>
+        <v>94.62616248946941</v>
       </c>
       <c r="D100">
-        <v>280.0076159722063</v>
+        <v>281.3891624894694</v>
       </c>
       <c r="E100">
-        <v>185.126</v>
+        <v>187.163</v>
       </c>
       <c r="F100">
-        <v>199.626</v>
+        <v>201.663</v>
       </c>
       <c r="G100">
         <v>14.9</v>
@@ -9487,28 +9487,28 @@
         <v>32.9</v>
       </c>
       <c r="M100">
-        <v>15.1316508</v>
+        <v>15.2860554</v>
       </c>
       <c r="N100">
-        <v>17.7683492</v>
+        <v>17.6139446</v>
       </c>
       <c r="O100">
-        <v>6.21892222</v>
+        <v>6.164880609999998</v>
       </c>
       <c r="P100">
-        <v>11.54942698</v>
+        <v>11.44906399</v>
       </c>
       <c r="Q100">
-        <v>16.44942698</v>
+        <v>16.34906399</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.200882759537152</v>
+        <v>12.29038625070785</v>
       </c>
       <c r="T100">
-        <v>30.24221242813998</v>
+        <v>60.16220950316431</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.174250545089238</v>
+        <v>2.152288418371164</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1716811625070786</v>
-      </c>
-      <c r="C101">
-        <v>94.62616248946941</v>
-      </c>
-      <c r="D101">
-        <v>281.3891624894694</v>
-      </c>
-      <c r="E101">
-        <v>187.163</v>
-      </c>
-      <c r="F101">
-        <v>201.663</v>
-      </c>
-      <c r="G101">
-        <v>14.9</v>
-      </c>
-      <c r="H101">
-        <v>189.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>37.8</v>
-      </c>
-      <c r="K101">
-        <v>4.899999999999999</v>
-      </c>
-      <c r="L101">
-        <v>32.9</v>
-      </c>
-      <c r="M101">
-        <v>15.2860554</v>
-      </c>
-      <c r="N101">
-        <v>17.6139446</v>
-      </c>
-      <c r="O101">
-        <v>6.164880609999998</v>
-      </c>
-      <c r="P101">
-        <v>11.44906399</v>
-      </c>
-      <c r="Q101">
-        <v>16.34906399</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>12.29038625070785</v>
-      </c>
-      <c r="T101">
-        <v>60.16220950316431</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.04927000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.152288418371164</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
